--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-11T11:43:09+00:00</t>
+    <t>2023-09-11T14:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-11T14:46:38+00:00</t>
+    <t>2023-09-12T10:01:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3136" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3473" uniqueCount="469">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-12T14:26:59+00:00</t>
+    <t>2023-09-13T08:02:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -486,225 +486,236 @@
     <t>Bundle.entry.resource</t>
   </si>
   <si>
+    <t xml:space="preserve">DocumentReference {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/dui-documentreference}
+</t>
+  </si>
+  <si>
+    <t>A reference to a document</t>
+  </si>
+  <si>
+    <t>A reference to a document of any kind for any purpose. Provides metadata about the document so that the document can be discovered and managed. The scope of a document is any seralized object with a mime-type, so includes formal patient centric documents (CDA), cliical notes, scanned paper, and non-patient specific documents like policy text.</t>
+  </si>
+  <si>
+    <t>Usually, this is used for documents other than those defined by FHIR.</t>
+  </si>
+  <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search</t>
+  </si>
+  <si>
+    <t>Search related information</t>
+  </si>
+  <si>
+    <t>Information about the search process that lead to the creation of this entry.</t>
+  </si>
+  <si>
+    <t>ele-1
+bdl-2</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.mode</t>
+  </si>
+  <si>
+    <t>match | include | outcome - why this is in the result set</t>
+  </si>
+  <si>
+    <t>Why this entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
+  </si>
+  <si>
+    <t>There is only one mode. In some corner cases, a resource may be included because it is both a match and an include. In these circumstances, 'match' takes precedence.</t>
+  </si>
+  <si>
+    <t>Why an entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/search-entry-mode|4.0.1</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Search ranking (between 0 and 1)</t>
+  </si>
+  <si>
+    <t>When searching, the server's search ranking score for the entry.</t>
+  </si>
+  <si>
+    <t>Servers are not required to return a ranking score. 1 is most relevant, and 0 is least relevant. Often, search results are sorted by score, but the client may specify a different sort order.
+See [Patient Match](http://hl7.org/fhir/R4/patient-operation-match.html) for the EMPI search which relates to this element.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request</t>
+  </si>
+  <si>
+    <t>Additional execution information (transaction/batch/history)</t>
+  </si>
+  <si>
+    <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
+  </si>
+  <si>
+    <t>ele-1
+bdl-3</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.method</t>
+  </si>
+  <si>
+    <t>GET | HEAD | POST | PUT | DELETE | PATCH</t>
+  </si>
+  <si>
+    <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
+  </si>
+  <si>
+    <t>HTTP verbs (in the HTTP command line). See [HTTP rfc](https://tools.ietf.org/html/rfc7231) for details.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/http-verb|4.0.1</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.url</t>
+  </si>
+  <si>
+    <t>URL for HTTP equivalent of this entry</t>
+  </si>
+  <si>
+    <t>The URL for this entry, relative to the root (the address to which the request is posted).</t>
+  </si>
+  <si>
+    <t>E.g. for a Patient Create, the method would be "POST" and the URL would be "Patient". For a Patient Update, the method would be PUT and the URL would be "Patient/[id]".</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifNoneMatch</t>
+  </si>
+  <si>
+    <t>For managing cache currency</t>
+  </si>
+  <si>
+    <t>If the ETag values match, return a 304 Not Modified status. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifModifiedSince</t>
+  </si>
+  <si>
+    <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
+  </si>
+  <si>
+    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifMatch</t>
+  </si>
+  <si>
+    <t>For managing update contention</t>
+  </si>
+  <si>
+    <t>Only perform the operation if the Etag value matches. For more information, see the API section ["Managing Resource Contention"](http://hl7.org/fhir/R4/http.html#concurrency).</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifNoneExist</t>
+  </si>
+  <si>
+    <t>For conditional creates</t>
+  </si>
+  <si>
+    <t>Instruct the server not to perform the create if a specified resource already exists. For further information, see the API documentation for ["Conditional Create"](http://hl7.org/fhir/R4/http.html#ccreate). This is just the query portion of the URL - what follows the "?" (not including the "?").</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response</t>
+  </si>
+  <si>
+    <t>Results of execution (transaction/batch/history)</t>
+  </si>
+  <si>
+    <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
+  </si>
+  <si>
+    <t>ele-1
+bdl-4</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.status</t>
+  </si>
+  <si>
+    <t>Status response code (text optional)</t>
+  </si>
+  <si>
+    <t>The status code returned by processing this entry. The status SHALL start with a 3 digit HTTP code (e.g. 404) and may contain the standard HTTP description associated with the status code.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.location</t>
+  </si>
+  <si>
+    <t>The location (if the operation returns a location)</t>
+  </si>
+  <si>
+    <t>The location header created by processing this operation, populated if the operation returns a location.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.etag</t>
+  </si>
+  <si>
+    <t>The Etag for the resource (if relevant)</t>
+  </si>
+  <si>
+    <t>The Etag for the resource, if the operation for the entry produced a versioned resource (see [Resource Metadata and Versioning](http://hl7.org/fhir/R4/http.html#versioning) and [Managing Resource Contention](http://hl7.org/fhir/R4/http.html#concurrency)).</t>
+  </si>
+  <si>
+    <t>Etags match the Resource.meta.versionId. The ETag has to match the version id in the header if a resource is included.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.lastModified</t>
+  </si>
+  <si>
+    <t>Server's date time modified</t>
+  </si>
+  <si>
+    <t>The date/time that the resource was modified on the server.</t>
+  </si>
+  <si>
+    <t>This has to match the same time in the meta header (meta.lastUpdated) if a resource is included.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.outcome</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resource
 </t>
   </si>
   <si>
-    <t>A resource in the bundle</t>
-  </si>
-  <si>
-    <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search</t>
-  </si>
-  <si>
-    <t>Search related information</t>
-  </si>
-  <si>
-    <t>Information about the search process that lead to the creation of this entry.</t>
-  </si>
-  <si>
-    <t>ele-1
-bdl-2</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.mode</t>
-  </si>
-  <si>
-    <t>match | include | outcome - why this is in the result set</t>
-  </si>
-  <si>
-    <t>Why this entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
-  </si>
-  <si>
-    <t>There is only one mode. In some corner cases, a resource may be included because it is both a match and an include. In these circumstances, 'match' takes precedence.</t>
-  </si>
-  <si>
-    <t>Why an entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/search-entry-mode|4.0.1</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
-    <t>Search ranking (between 0 and 1)</t>
-  </si>
-  <si>
-    <t>When searching, the server's search ranking score for the entry.</t>
-  </si>
-  <si>
-    <t>Servers are not required to return a ranking score. 1 is most relevant, and 0 is least relevant. Often, search results are sorted by score, but the client may specify a different sort order.
-See [Patient Match](http://hl7.org/fhir/R4/patient-operation-match.html) for the EMPI search which relates to this element.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request</t>
-  </si>
-  <si>
-    <t>Additional execution information (transaction/batch/history)</t>
-  </si>
-  <si>
-    <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
-  </si>
-  <si>
-    <t>ele-1
-bdl-3</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.method</t>
-  </si>
-  <si>
-    <t>GET | HEAD | POST | PUT | DELETE | PATCH</t>
-  </si>
-  <si>
-    <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
-  </si>
-  <si>
-    <t>HTTP verbs (in the HTTP command line). See [HTTP rfc](https://tools.ietf.org/html/rfc7231) for details.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/http-verb|4.0.1</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.url</t>
-  </si>
-  <si>
-    <t>URL for HTTP equivalent of this entry</t>
-  </si>
-  <si>
-    <t>The URL for this entry, relative to the root (the address to which the request is posted).</t>
-  </si>
-  <si>
-    <t>E.g. for a Patient Create, the method would be "POST" and the URL would be "Patient". For a Patient Update, the method would be PUT and the URL would be "Patient/[id]".</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifNoneMatch</t>
-  </si>
-  <si>
-    <t>For managing cache currency</t>
-  </si>
-  <si>
-    <t>If the ETag values match, return a 304 Not Modified status. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifModifiedSince</t>
-  </si>
-  <si>
-    <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
-  </si>
-  <si>
-    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifMatch</t>
-  </si>
-  <si>
-    <t>For managing update contention</t>
-  </si>
-  <si>
-    <t>Only perform the operation if the Etag value matches. For more information, see the API section ["Managing Resource Contention"](http://hl7.org/fhir/R4/http.html#concurrency).</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifNoneExist</t>
-  </si>
-  <si>
-    <t>For conditional creates</t>
-  </si>
-  <si>
-    <t>Instruct the server not to perform the create if a specified resource already exists. For further information, see the API documentation for ["Conditional Create"](http://hl7.org/fhir/R4/http.html#ccreate). This is just the query portion of the URL - what follows the "?" (not including the "?").</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response</t>
-  </si>
-  <si>
-    <t>Results of execution (transaction/batch/history)</t>
-  </si>
-  <si>
-    <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
-  </si>
-  <si>
-    <t>ele-1
-bdl-4</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.status</t>
-  </si>
-  <si>
-    <t>Status response code (text optional)</t>
-  </si>
-  <si>
-    <t>The status code returned by processing this entry. The status SHALL start with a 3 digit HTTP code (e.g. 404) and may contain the standard HTTP description associated with the status code.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.location</t>
-  </si>
-  <si>
-    <t>The location (if the operation returns a location)</t>
-  </si>
-  <si>
-    <t>The location header created by processing this operation, populated if the operation returns a location.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.etag</t>
-  </si>
-  <si>
-    <t>The Etag for the resource (if relevant)</t>
-  </si>
-  <si>
-    <t>The Etag for the resource, if the operation for the entry produced a versioned resource (see [Resource Metadata and Versioning](http://hl7.org/fhir/R4/http.html#versioning) and [Managing Resource Contention](http://hl7.org/fhir/R4/http.html#concurrency)).</t>
-  </si>
-  <si>
-    <t>Etags match the Resource.meta.versionId. The ETag has to match the version id in the header if a resource is included.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.lastModified</t>
-  </si>
-  <si>
-    <t>Server's date time modified</t>
-  </si>
-  <si>
-    <t>The date/time that the resource was modified on the server.</t>
-  </si>
-  <si>
-    <t>This has to match the same time in the meta header (meta.lastUpdated) if a resource is included.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.outcome</t>
-  </si>
-  <si>
     <t>OperationOutcome with hints and warnings (for batch/transaction)</t>
   </si>
   <si>
@@ -743,26 +754,13 @@
     <t>DUIDocumentReference</t>
   </si>
   <si>
-    <t>Profil générique créé dans le contexte du transfert de données DUI pour véhiculer le dossier au format CDA.</t>
+    <t>Profil générique créé dans le contexte du transfert de données DUI pour véhiculer le dossier au format CDA, inclus dans DocumentReference.attachment.data.</t>
   </si>
   <si>
     <t>DocumentReference</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/StructureDefinition/DocumentReference</t>
-  </si>
-  <si>
-    <t>A reference to a document</t>
-  </si>
-  <si>
-    <t>A reference to a document of any kind for any purpose. Provides metadata about the document so that the document can be discovered and managed. The scope of a document is any seralized object with a mime-type, so includes formal patient centric documents (CDA), cliical notes, scanned paper, and non-patient specific documents like policy text.</t>
-  </si>
-  <si>
-    <t>Usually, this is used for documents other than those defined by FHIR.</t>
-  </si>
-  <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>DocumentReference.id</t>
@@ -1128,7 +1126,7 @@
     <t>DocumentReference.content</t>
   </si>
   <si>
-    <t>Document referenced</t>
+    <t>Document contenu.</t>
   </si>
   <si>
     <t>The document and format referenced. There may be multiple content element repetitions, each with a different format.</t>
@@ -1161,6 +1159,174 @@
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 att-1:If the Attachment has data, it SHALL have a contentType {data.empty() or contentType.exists()}</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.contentType</t>
+  </si>
+  <si>
+    <t>Mime type of the content, with charset etc.</t>
+  </si>
+  <si>
+    <t>Identifies the type of the data in the attachment and allows a method to be chosen to interpret or render the data. Includes mime type parameters such as charset where appropriate.</t>
+  </si>
+  <si>
+    <t>Processors of the data need to be able to know how to interpret the data.</t>
+  </si>
+  <si>
+    <t>text/plain; charset=UTF-8, image/png</t>
+  </si>
+  <si>
+    <t>The mime type of an attachment. Any valid mime type is allowed.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/mimetypes|4.0.1</t>
+  </si>
+  <si>
+    <t>Attachment.contentType</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.language</t>
+  </si>
+  <si>
+    <t>Human language of the content (BCP-47)</t>
+  </si>
+  <si>
+    <t>The human language of the content. The value can be any valid value according to BCP 47.</t>
+  </si>
+  <si>
+    <t>Users need to be able to choose between the languages in a set of attachments.</t>
+  </si>
+  <si>
+    <t>en-AU</t>
+  </si>
+  <si>
+    <t>Attachment.language</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base64Binary
+</t>
+  </si>
+  <si>
+    <t>Le document CDA est contenu dans l'élément .data au format base64.</t>
+  </si>
+  <si>
+    <t>The actual data of the attachment - a sequence of bytes, base64 encoded.</t>
+  </si>
+  <si>
+    <t>The base64-encoded data SHALL be expressed in the same character set as the base resource XML or JSON.</t>
+  </si>
+  <si>
+    <t>The data needs to able to be transmitted inline.</t>
+  </si>
+  <si>
+    <t>Attachment.data</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">url
+</t>
+  </si>
+  <si>
+    <t>Uri where the data can be found</t>
+  </si>
+  <si>
+    <t>A location where the data can be accessed.</t>
+  </si>
+  <si>
+    <t>If both data and url are provided, the url SHALL point to the same content as the data contains. Urls may be relative references or may reference transient locations such as a wrapping envelope using cid: though this has ramifications for using signatures. Relative URLs are interpreted relative to the service url, like a resource reference, rather than relative to the resource itself. If a URL is provided, it SHALL resolve to actual data.</t>
+  </si>
+  <si>
+    <t>The data needs to be transmitted by reference.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/logo-small.png</t>
+  </si>
+  <si>
+    <t>Attachment.url</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.size</t>
+  </si>
+  <si>
+    <t>Number of bytes of content (if url provided)</t>
+  </si>
+  <si>
+    <t>The number of bytes of data that make up this attachment (before base64 encoding, if that is done).</t>
+  </si>
+  <si>
+    <t>The number of bytes is redundant if the data is provided as a base64binary, but is useful if the data is provided as a url reference.</t>
+  </si>
+  <si>
+    <t>Representing the size allows applications to determine whether they should fetch the content automatically in advance, or refuse to fetch it at all.</t>
+  </si>
+  <si>
+    <t>Attachment.size</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.hash</t>
+  </si>
+  <si>
+    <t>Hash of the data (sha-1, base64ed)</t>
+  </si>
+  <si>
+    <t>The calculated hash of the data using SHA-1. Represented using base64.</t>
+  </si>
+  <si>
+    <t>The hash is calculated on the data prior to base64 encoding, if the data is based64 encoded. The hash is not intended to support digital signatures. Where protection against malicious threats a digital signature should be considered, see [Provenance.signature](http://hl7.org/fhir/R4/provenance-definitions.html#Provenance.signature) for mechanism to protect a resource with a digital signature.</t>
+  </si>
+  <si>
+    <t>Included so that applications can verify that the contents of a location have not changed due to technical failures (e.g., storage rot, transport glitch, incorrect version).</t>
+  </si>
+  <si>
+    <t>Attachment.hash</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.title</t>
+  </si>
+  <si>
+    <t>Label to display in place of the data</t>
+  </si>
+  <si>
+    <t>A label or set of text to display in place of the data.</t>
+  </si>
+  <si>
+    <t>Applications need a label to display to a human user in place of the actual data if the data cannot be rendered or perceived by the viewer.</t>
+  </si>
+  <si>
+    <t>Official Corporate Logo</t>
+  </si>
+  <si>
+    <t>Attachment.title</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.creation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date attachment was first created</t>
+  </si>
+  <si>
+    <t>The date that the attachment was first created.</t>
+  </si>
+  <si>
+    <t>This is often tracked as an integrity issue for use of the attachment.</t>
+  </si>
+  <si>
+    <t>Attachment.creation</t>
   </si>
   <si>
     <t>DocumentReference.content.format</t>
@@ -1629,7 +1795,7 @@
         <v>2</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23">
@@ -1637,7 +1803,7 @@
         <v>4</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24">
@@ -1653,7 +1819,7 @@
         <v>8</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26">
@@ -1705,7 +1871,7 @@
         <v>20</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="33">
@@ -1741,7 +1907,7 @@
         <v>28</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38">
@@ -1749,7 +1915,7 @@
         <v>30</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39">
@@ -1775,16 +1941,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK93"/>
+  <dimension ref="A1:AK103"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.23828125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="46.23828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="2" max="2" width="50.828125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="50.828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="39.9140625" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="2.2109375" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="2.2109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="2.1640625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="2.1640625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1795,7 +1961,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="20" max="20" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="35.69140625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="1.04296875" customWidth="true" bestFit="true"/>
@@ -4039,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>146</v>
@@ -4050,7 +4216,9 @@
       <c r="N22" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="O22" s="2"/>
+      <c r="O22" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P22" s="2"/>
       <c r="Q22" t="s" s="2">
         <v>36</v>
@@ -4111,7 +4279,7 @@
         <v>36</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>36</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23">
@@ -4119,10 +4287,10 @@
         <v>3</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
@@ -4148,10 +4316,10 @@
         <v>97</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -4202,7 +4370,7 @@
         <v>36</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>37</v>
@@ -4211,7 +4379,7 @@
         <v>44</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>57</v>
@@ -4222,10 +4390,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
@@ -4325,10 +4493,10 @@
         <v>3</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
@@ -4430,10 +4598,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
@@ -4537,10 +4705,10 @@
         <v>3</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
@@ -4566,13 +4734,13 @@
         <v>65</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P27" s="2"/>
       <c r="Q27" t="s" s="2">
@@ -4601,10 +4769,10 @@
         <v>82</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AB27" t="s" s="2">
         <v>36</v>
@@ -4622,7 +4790,7 @@
         <v>36</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>37</v>
@@ -4642,10 +4810,10 @@
         <v>3</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
@@ -4668,16 +4836,16 @@
         <v>45</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="P28" s="2"/>
       <c r="Q28" t="s" s="2">
@@ -4727,7 +4895,7 @@
         <v>36</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>37</v>
@@ -4747,10 +4915,10 @@
         <v>3</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -4776,10 +4944,10 @@
         <v>97</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -4830,7 +4998,7 @@
         <v>36</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>37</v>
@@ -4839,7 +5007,7 @@
         <v>44</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>57</v>
@@ -4850,10 +5018,10 @@
         <v>3</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -4953,10 +5121,10 @@
         <v>3</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -5058,10 +5226,10 @@
         <v>3</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -5165,10 +5333,10 @@
         <v>3</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -5194,10 +5362,10 @@
         <v>65</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="O33" t="s" s="2">
         <v>126</v>
@@ -5229,10 +5397,10 @@
         <v>82</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AB33" t="s" s="2">
         <v>36</v>
@@ -5250,7 +5418,7 @@
         <v>36</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>44</v>
@@ -5270,10 +5438,10 @@
         <v>3</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -5299,13 +5467,13 @@
         <v>59</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="P34" s="2"/>
       <c r="Q34" t="s" s="2">
@@ -5355,7 +5523,7 @@
         <v>36</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>44</v>
@@ -5375,10 +5543,10 @@
         <v>3</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -5404,10 +5572,10 @@
         <v>102</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O35" t="s" s="2">
         <v>126</v>
@@ -5460,7 +5628,7 @@
         <v>36</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>37</v>
@@ -5480,10 +5648,10 @@
         <v>3</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -5509,13 +5677,13 @@
         <v>86</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P36" s="2"/>
       <c r="Q36" t="s" s="2">
@@ -5565,7 +5733,7 @@
         <v>36</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>37</v>
@@ -5585,10 +5753,10 @@
         <v>3</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -5614,10 +5782,10 @@
         <v>102</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O37" t="s" s="2">
         <v>126</v>
@@ -5670,7 +5838,7 @@
         <v>36</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>37</v>
@@ -5690,10 +5858,10 @@
         <v>3</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -5719,10 +5887,10 @@
         <v>102</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>126</v>
@@ -5775,7 +5943,7 @@
         <v>36</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>37</v>
@@ -5795,10 +5963,10 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -5824,10 +5992,10 @@
         <v>97</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
@@ -5878,7 +6046,7 @@
         <v>36</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>37</v>
@@ -5887,7 +6055,7 @@
         <v>44</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>57</v>
@@ -5898,10 +6066,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6001,10 +6169,10 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -6106,10 +6274,10 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -6213,10 +6381,10 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -6242,10 +6410,10 @@
         <v>102</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O43" t="s" s="2">
         <v>126</v>
@@ -6298,7 +6466,7 @@
         <v>36</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>44</v>
@@ -6318,10 +6486,10 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
@@ -6347,10 +6515,10 @@
         <v>59</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O44" t="s" s="2">
         <v>130</v>
@@ -6403,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>37</v>
@@ -6423,10 +6591,10 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -6452,13 +6620,13 @@
         <v>102</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P45" s="2"/>
       <c r="Q45" t="s" s="2">
@@ -6508,7 +6676,7 @@
         <v>36</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>37</v>
@@ -6528,10 +6696,10 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -6557,13 +6725,13 @@
         <v>86</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="P46" s="2"/>
       <c r="Q46" t="s" s="2">
@@ -6613,7 +6781,7 @@
         <v>36</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>37</v>
@@ -6633,10 +6801,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -6659,16 +6827,16 @@
         <v>45</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>146</v>
+        <v>219</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="P47" s="2"/>
       <c r="Q47" t="s" s="2">
@@ -6718,7 +6886,7 @@
         <v>36</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>37</v>
@@ -6738,10 +6906,10 @@
         <v>3</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -6764,19 +6932,19 @@
         <v>45</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P48" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q48" t="s" s="2">
         <v>36</v>
@@ -6825,7 +6993,7 @@
         <v>36</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>37</v>
@@ -6842,13 +7010,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -6874,13 +7042,13 @@
         <v>39</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>232</v>
+        <v>147</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>233</v>
+        <v>148</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>234</v>
+        <v>149</v>
       </c>
       <c r="P49" s="2"/>
       <c r="Q49" t="s" s="2">
@@ -6930,7 +7098,7 @@
         <v>36</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>37</v>
@@ -6942,18 +7110,18 @@
         <v>36</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>235</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7052,13 +7220,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -7155,13 +7323,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -7260,13 +7428,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -7365,17 +7533,17 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" t="s" s="2">
@@ -7394,16 +7562,16 @@
         <v>36</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="P54" s="2"/>
       <c r="Q54" t="s" s="2">
@@ -7453,7 +7621,7 @@
         <v>36</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>37</v>
@@ -7470,17 +7638,17 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" t="s" s="2">
@@ -7499,16 +7667,16 @@
         <v>36</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>146</v>
+        <v>219</v>
       </c>
       <c r="M55" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="P55" s="2"/>
       <c r="Q55" t="s" s="2">
@@ -7558,7 +7726,7 @@
         <v>36</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>37</v>
@@ -7575,13 +7743,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -7610,7 +7778,7 @@
         <v>109</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>111</v>
@@ -7663,7 +7831,7 @@
         <v>114</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>37</v>
@@ -7680,13 +7848,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -7712,10 +7880,10 @@
         <v>108</v>
       </c>
       <c r="M57" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>111</v>
@@ -7770,7 +7938,7 @@
         <v>114</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>37</v>
@@ -7787,13 +7955,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -7819,16 +7987,16 @@
         <v>74</v>
       </c>
       <c r="M58" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="O58" t="s" s="2">
+      <c r="P58" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="P58" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="Q58" t="s" s="2">
         <v>36</v>
@@ -7877,7 +8045,7 @@
         <v>36</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>37</v>
@@ -7894,13 +8062,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -7926,10 +8094,10 @@
         <v>74</v>
       </c>
       <c r="M59" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" s="2"/>
@@ -7980,7 +8148,7 @@
         <v>36</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>37</v>
@@ -7997,13 +8165,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -8029,13 +8197,13 @@
         <v>65</v>
       </c>
       <c r="M60" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="P60" s="2"/>
       <c r="Q60" t="s" s="2">
@@ -8064,11 +8232,11 @@
         <v>82</v>
       </c>
       <c r="Z60" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AA60" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AA60" t="s" s="2">
-        <v>273</v>
-      </c>
       <c r="AB60" t="s" s="2">
         <v>36</v>
       </c>
@@ -8085,7 +8253,7 @@
         <v>36</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>44</v>
@@ -8102,13 +8270,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -8134,13 +8302,13 @@
         <v>65</v>
       </c>
       <c r="M61" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P61" s="2"/>
       <c r="Q61" t="s" s="2">
@@ -8169,11 +8337,11 @@
         <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AA61" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AA61" t="s" s="2">
-        <v>279</v>
-      </c>
       <c r="AB61" t="s" s="2">
         <v>36</v>
       </c>
@@ -8190,7 +8358,7 @@
         <v>36</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>37</v>
@@ -8207,13 +8375,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -8236,16 +8404,16 @@
         <v>45</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="P62" s="2"/>
       <c r="Q62" t="s" s="2">
@@ -8274,11 +8442,11 @@
         <v>69</v>
       </c>
       <c r="Z62" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AA62" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AA62" t="s" s="2">
-        <v>286</v>
-      </c>
       <c r="AB62" t="s" s="2">
         <v>36</v>
       </c>
@@ -8295,7 +8463,7 @@
         <v>36</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>37</v>
@@ -8312,17 +8480,17 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" t="s" s="2">
@@ -8341,16 +8509,16 @@
         <v>45</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M63" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" t="s" s="2">
@@ -8376,14 +8544,14 @@
         <v>36</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="Z63" t="s" s="2">
+      <c r="AA63" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AA63" t="s" s="2">
-        <v>294</v>
-      </c>
       <c r="AB63" t="s" s="2">
         <v>36</v>
       </c>
@@ -8400,7 +8568,7 @@
         <v>36</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>37</v>
@@ -8417,13 +8585,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -8446,16 +8614,16 @@
         <v>45</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="P64" s="2"/>
       <c r="Q64" t="s" s="2">
@@ -8505,7 +8673,7 @@
         <v>36</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>37</v>
@@ -8517,22 +8685,22 @@
         <v>56</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" t="s" s="2">
@@ -8554,13 +8722,13 @@
         <v>86</v>
       </c>
       <c r="M65" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="P65" s="2"/>
       <c r="Q65" t="s" s="2">
@@ -8610,7 +8778,7 @@
         <v>36</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>37</v>
@@ -8627,13 +8795,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -8656,16 +8824,16 @@
         <v>45</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="P66" s="2"/>
       <c r="Q66" t="s" s="2">
@@ -8715,7 +8883,7 @@
         <v>36</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>37</v>
@@ -8727,18 +8895,18 @@
         <v>56</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -8761,16 +8929,16 @@
         <v>36</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" t="s" s="2">
@@ -8820,7 +8988,7 @@
         <v>36</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>37</v>
@@ -8832,18 +9000,18 @@
         <v>56</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -8866,16 +9034,16 @@
         <v>36</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="P68" s="2"/>
       <c r="Q68" t="s" s="2">
@@ -8925,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>37</v>
@@ -8937,18 +9105,18 @@
         <v>56</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -8974,13 +9142,13 @@
         <v>97</v>
       </c>
       <c r="M69" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="P69" s="2"/>
       <c r="Q69" t="s" s="2">
@@ -9030,7 +9198,7 @@
         <v>36</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>37</v>
@@ -9047,13 +9215,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -9150,13 +9318,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -9255,13 +9423,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -9362,13 +9530,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -9394,13 +9562,13 @@
         <v>65</v>
       </c>
       <c r="M73" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P73" s="2"/>
       <c r="Q73" t="s" s="2">
@@ -9429,11 +9597,11 @@
         <v>82</v>
       </c>
       <c r="Z73" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AA73" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AA73" t="s" s="2">
-        <v>333</v>
-      </c>
       <c r="AB73" t="s" s="2">
         <v>36</v>
       </c>
@@ -9450,7 +9618,7 @@
         <v>36</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>44</v>
@@ -9467,13 +9635,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -9496,16 +9664,16 @@
         <v>45</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="N74" t="s" s="2">
-        <v>337</v>
-      </c>
       <c r="O74" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P74" s="2"/>
       <c r="Q74" t="s" s="2">
@@ -9555,7 +9723,7 @@
         <v>36</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>44</v>
@@ -9567,18 +9735,18 @@
         <v>56</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -9604,16 +9772,16 @@
         <v>102</v>
       </c>
       <c r="M75" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="O75" t="s" s="2">
+      <c r="P75" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="Q75" t="s" s="2">
         <v>36</v>
@@ -9662,7 +9830,7 @@
         <v>36</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>37</v>
@@ -9679,13 +9847,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -9708,19 +9876,19 @@
         <v>45</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M76" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="O76" t="s" s="2">
+      <c r="P76" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="P76" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="Q76" t="s" s="2">
         <v>36</v>
@@ -9745,14 +9913,14 @@
         <v>36</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="Z76" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="Z76" t="s" s="2">
+      <c r="AA76" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AA76" t="s" s="2">
-        <v>350</v>
-      </c>
       <c r="AB76" t="s" s="2">
         <v>36</v>
       </c>
@@ -9769,7 +9937,7 @@
         <v>36</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>37</v>
@@ -9786,13 +9954,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -9806,7 +9974,7 @@
         <v>44</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>36</v>
@@ -9818,10 +9986,10 @@
         <v>97</v>
       </c>
       <c r="M77" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" s="2"/>
@@ -9872,7 +10040,7 @@
         <v>36</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>44</v>
@@ -9889,13 +10057,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -9992,13 +10160,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -10097,13 +10265,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -10204,13 +10372,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -10233,16 +10401,16 @@
         <v>45</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="P81" s="2"/>
       <c r="Q81" t="s" s="2">
@@ -10292,7 +10460,7 @@
         <v>36</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>44</v>
@@ -10304,18 +10472,18 @@
         <v>56</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -10335,20 +10503,18 @@
         <v>36</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>364</v>
+        <v>102</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>365</v>
+        <v>103</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" s="2"/>
       <c r="Q82" t="s" s="2">
         <v>36</v>
@@ -10373,13 +10539,13 @@
         <v>36</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>368</v>
+        <v>36</v>
       </c>
       <c r="AA82" t="s" s="2">
-        <v>369</v>
+        <v>36</v>
       </c>
       <c r="AB82" t="s" s="2">
         <v>36</v>
@@ -10397,7 +10563,7 @@
         <v>36</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>363</v>
+        <v>105</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>37</v>
@@ -10406,32 +10572,32 @@
         <v>44</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>57</v>
+        <v>36</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" t="s" s="2">
         <v>37</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>36</v>
@@ -10440,19 +10606,19 @@
         <v>36</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>371</v>
+        <v>109</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>372</v>
+        <v>110</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>373</v>
+        <v>111</v>
       </c>
       <c r="P83" s="2"/>
       <c r="Q83" t="s" s="2">
@@ -10490,42 +10656,42 @@
         <v>36</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="AD83" t="s" s="2">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="AE83" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>370</v>
+        <v>115</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -10545,19 +10711,23 @@
         <v>36</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>103</v>
+        <v>365</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O84" s="2"/>
-      <c r="P84" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="Q84" t="s" s="2">
         <v>36</v>
       </c>
@@ -10569,7 +10739,7 @@
         <v>36</v>
       </c>
       <c r="U84" t="s" s="2">
-        <v>36</v>
+        <v>368</v>
       </c>
       <c r="V84" t="s" s="2">
         <v>36</v>
@@ -10581,13 +10751,13 @@
         <v>36</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>36</v>
+        <v>369</v>
       </c>
       <c r="AA84" t="s" s="2">
-        <v>36</v>
+        <v>370</v>
       </c>
       <c r="AB84" t="s" s="2">
         <v>36</v>
@@ -10605,7 +10775,7 @@
         <v>36</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>105</v>
+        <v>371</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>37</v>
@@ -10614,32 +10784,32 @@
         <v>44</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>36</v>
+        <v>57</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" t="s" s="2">
         <v>37</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>36</v>
@@ -10648,21 +10818,23 @@
         <v>36</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>109</v>
+        <v>373</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>110</v>
+        <v>374</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="P85" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="Q85" t="s" s="2">
         <v>36</v>
       </c>
@@ -10674,7 +10846,7 @@
         <v>36</v>
       </c>
       <c r="U85" t="s" s="2">
-        <v>36</v>
+        <v>376</v>
       </c>
       <c r="V85" t="s" s="2">
         <v>36</v>
@@ -10686,89 +10858,89 @@
         <v>36</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AA85" t="s" s="2">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="AB85" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="AD85" t="s" s="2">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="AE85" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>115</v>
+        <v>377</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
-        <v>118</v>
+        <v>36</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>108</v>
+        <v>379</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>119</v>
+        <v>380</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>120</v>
+        <v>381</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>111</v>
+        <v>382</v>
       </c>
       <c r="P86" t="s" s="2">
-        <v>121</v>
+        <v>383</v>
       </c>
       <c r="Q86" t="s" s="2">
         <v>36</v>
@@ -10817,30 +10989,30 @@
         <v>36</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>122</v>
+        <v>384</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -10851,7 +11023,7 @@
         <v>37</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>36</v>
@@ -10860,21 +11032,23 @@
         <v>36</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="P87" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="P87" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="Q87" t="s" s="2">
         <v>36</v>
       </c>
@@ -10886,7 +11060,7 @@
         <v>36</v>
       </c>
       <c r="U87" t="s" s="2">
-        <v>36</v>
+        <v>391</v>
       </c>
       <c r="V87" t="s" s="2">
         <v>36</v>
@@ -10922,30 +11096,30 @@
         <v>36</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>300</v>
+        <v>57</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -10956,7 +11130,7 @@
         <v>37</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>36</v>
@@ -10965,21 +11139,23 @@
         <v>36</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>281</v>
+        <v>91</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="P88" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="Q88" t="s" s="2">
         <v>36</v>
       </c>
@@ -11003,13 +11179,13 @@
         <v>36</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>292</v>
+        <v>36</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>385</v>
+        <v>36</v>
       </c>
       <c r="AA88" t="s" s="2">
-        <v>386</v>
+        <v>36</v>
       </c>
       <c r="AB88" t="s" s="2">
         <v>36</v>
@@ -11027,13 +11203,13 @@
         <v>36</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>56</v>
@@ -11044,13 +11220,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -11073,18 +11249,20 @@
         <v>45</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="P89" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="Q89" t="s" s="2">
         <v>36</v>
       </c>
@@ -11132,7 +11310,7 @@
         <v>36</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>387</v>
+        <v>404</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>37</v>
@@ -11144,18 +11322,18 @@
         <v>56</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>392</v>
+        <v>57</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -11175,21 +11353,23 @@
         <v>36</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>281</v>
+        <v>102</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="P90" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="P90" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="Q90" t="s" s="2">
         <v>36</v>
       </c>
@@ -11201,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="U90" t="s" s="2">
-        <v>36</v>
+        <v>409</v>
       </c>
       <c r="V90" t="s" s="2">
         <v>36</v>
@@ -11213,13 +11393,13 @@
         <v>36</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>292</v>
+        <v>36</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>397</v>
+        <v>36</v>
       </c>
       <c r="AA90" t="s" s="2">
-        <v>398</v>
+        <v>36</v>
       </c>
       <c r="AB90" t="s" s="2">
         <v>36</v>
@@ -11237,7 +11417,7 @@
         <v>36</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>37</v>
@@ -11254,13 +11434,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -11280,22 +11460,20 @@
         <v>36</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>281</v>
+        <v>412</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="Q91" t="s" s="2">
         <v>36</v>
@@ -11320,13 +11498,13 @@
         <v>36</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>292</v>
+        <v>36</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>404</v>
+        <v>36</v>
       </c>
       <c r="AA91" t="s" s="2">
-        <v>405</v>
+        <v>36</v>
       </c>
       <c r="AB91" t="s" s="2">
         <v>36</v>
@@ -11344,7 +11522,7 @@
         <v>36</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>37</v>
@@ -11361,13 +11539,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -11387,19 +11565,19 @@
         <v>36</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>299</v>
+        <v>421</v>
       </c>
       <c r="P92" s="2"/>
       <c r="Q92" t="s" s="2">
@@ -11425,13 +11603,13 @@
         <v>36</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>36</v>
+        <v>422</v>
       </c>
       <c r="AA92" t="s" s="2">
-        <v>36</v>
+        <v>423</v>
       </c>
       <c r="AB92" t="s" s="2">
         <v>36</v>
@@ -11449,7 +11627,7 @@
         <v>36</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>37</v>
@@ -11461,18 +11639,18 @@
         <v>56</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>300</v>
+        <v>57</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -11483,7 +11661,7 @@
         <v>37</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>36</v>
@@ -11492,19 +11670,19 @@
         <v>36</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>411</v>
+        <v>97</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="P93" s="2"/>
       <c r="Q93" t="s" s="2">
@@ -11554,19 +11732,1071 @@
         <v>36</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>300</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="D94" s="2"/>
+      <c r="E94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F94" s="2"/>
+      <c r="G94" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="O94" s="2"/>
+      <c r="P94" s="2"/>
+      <c r="Q94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="R94" s="2"/>
+      <c r="S94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="D95" s="2"/>
+      <c r="E95" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="F95" s="2"/>
+      <c r="G95" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="P95" s="2"/>
+      <c r="Q95" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="R95" s="2"/>
+      <c r="S95" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="D96" s="2"/>
+      <c r="E96" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="F96" s="2"/>
+      <c r="G96" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="Q96" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="R96" s="2"/>
+      <c r="S96" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="D97" s="2"/>
+      <c r="E97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F97" s="2"/>
+      <c r="G97" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="P97" s="2"/>
+      <c r="Q97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="R97" s="2"/>
+      <c r="S97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="D98" s="2"/>
+      <c r="E98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F98" s="2"/>
+      <c r="G98" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="P98" s="2"/>
+      <c r="Q98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="R98" s="2"/>
+      <c r="S98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C99" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="D99" s="2"/>
+      <c r="E99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F99" s="2"/>
+      <c r="G99" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="P99" s="2"/>
+      <c r="Q99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="R99" s="2"/>
+      <c r="S99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="D100" s="2"/>
+      <c r="E100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F100" s="2"/>
+      <c r="G100" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="P100" s="2"/>
+      <c r="Q100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="R100" s="2"/>
+      <c r="S100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C101" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="D101" s="2"/>
+      <c r="E101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F101" s="2"/>
+      <c r="G101" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="Q101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="R101" s="2"/>
+      <c r="S101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="D102" s="2"/>
+      <c r="E102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F102" s="2"/>
+      <c r="G102" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="P102" s="2"/>
+      <c r="Q102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="R102" s="2"/>
+      <c r="S102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="D103" s="2"/>
+      <c r="E103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F103" s="2"/>
+      <c r="G103" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="P103" s="2"/>
+      <c r="Q103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="R103" s="2"/>
+      <c r="S103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>299</v>
       </c>
     </row>
   </sheetData>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-13T08:02:35+00:00</t>
+    <t>2023-09-13T10:23:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-13T10:23:45+00:00</t>
+    <t>2023-09-13T10:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-13T10:41:32+00:00</t>
+    <t>2023-09-13T13:19:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-13T13:19:45+00:00</t>
+    <t>2023-09-13T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-13T14:55:53+00:00</t>
+    <t>2023-09-14T12:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-14T12:40:46+00:00</t>
+    <t>2023-09-14T13:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-14T13:51:30+00:00</t>
+    <t>2023-09-15T08:58:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3473" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3732" uniqueCount="506">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-15T08:58:52+00:00</t>
+    <t>2023-09-18T08:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -754,6 +754,9 @@
     <t>DUIDocumentReference</t>
   </si>
   <si>
+    <t>DUI Document Reference</t>
+  </si>
+  <si>
     <t>Profil générique créé dans le contexte du transfert de données DUI pour véhiculer le dossier au format CDA, inclus dans DocumentReference.attachment.data.</t>
   </si>
   <si>
@@ -767,6 +770,129 @@
   </si>
   <si>
     <t>DocumentReference.meta</t>
+  </si>
+  <si>
+    <t>DocumentReference.meta.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.meta.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.meta.versionId</t>
+  </si>
+  <si>
+    <t>Numéro de version de la fiche d’un document attribué par le système cible. La valeur de la métadonnée version est égale à 1 pour la première version de la fiche. Cet élément est requis lorsque le flux envoyé correspond à une mise à jour des données d’une fiche.</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>DocumentReference.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>DocumentReference.meta.source</t>
+  </si>
+  <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>DocumentReference.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>DocumentReference.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>DocumentReference.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
   </si>
   <si>
     <t>DocumentReference.implicitRules</t>
@@ -842,7 +968,7 @@
     <t>DocumentReference.masterIdentifier</t>
   </si>
   <si>
-    <t>Master Version Specific Identifier</t>
+    <t>Représente l’identifiant unique global affecté au document par son créateur. Il est utilisable comme référence externe dans d’autres documents.</t>
   </si>
   <si>
     <t>Document identifier as assigned by the source of the document. This identifier is specific to this version of the document. This unique identifier may be used elsewhere to identify this version of the document.</t>
@@ -876,6 +1002,9 @@
 This element is labeled as a modifier because the status contains the codes that mark the document or reference as not currently valid.</t>
   </si>
   <si>
+    <t>current</t>
+  </si>
+  <si>
     <t>The status of the document reference.</t>
   </si>
   <si>
@@ -910,16 +1039,22 @@
     <t>Kind of document (LOINC if possible)</t>
   </si>
   <si>
-    <t>Specifies the particular kind of document referenced  (e.g. History and Physical, Discharge Summary, Progress Note). This usually equates to the purpose of making the document referenced.</t>
+    <t>Représente le type du document.</t>
   </si>
   <si>
     <t>Key metadata element describing the document that describes he exact type of document. Helps humans to assess whether the document is of interest when viewing a list of documents.</t>
   </si>
   <si>
-    <t>Precise type of clinical document.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-doc-typecodes</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J07-XdsTypeCode-CISIS/FHIR/JDV-J07-XdsTypeCode-CISIS</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+constr-bind-type:Les valeurs possibles pour cet élément doivent provenir d’une des terminologies de référence suivantes :
+ TRE_A05-TypeDocComplementaireCISIS, OID : 1.2.250.1.213.1.1.4.12
+ TRE_A04-TypeDocument-LOINC, OID : 2.16.840.1.113883.6.1
+ TRE_A12-NomenclatureASTM, OID : ASTM
+Les valeurs possibles peuvent être restreintes en fonction du jeu de valeurs correspondant mis à disposition par le projet (exemple : JDV_J66-TypeCode-DMP).
+En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J07-XdsTypeCode-CISIS peut être utilisé. {f:type}</t>
   </si>
   <si>
     <t>DocumentReference.category</t>
@@ -929,7 +1064,7 @@
 </t>
   </si>
   <si>
-    <t>Categorization of document</t>
+    <t>Représente la classe du document (compte rendu, imagerie médicale, traitement, certificat,...).</t>
   </si>
   <si>
     <t>A categorization for the type of document referenced - helps for indexing and searching. This may be implied by or derived from the code specified in the DocumentReference.type.</t>
@@ -938,23 +1073,25 @@
     <t>Key metadata element describing the the category or classification of the document. This is a broader perspective that groups similar documents based on how they would be used. This is a primary key used in searching.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>High-level kind of a clinical document at a macro level.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/document-classcodes</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J06-XdsClassCode-CISIS/FHIR/JDV-J06-XdsClassCode-CISIS</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+constr-bind-category:Les valeurs possibles pour cet élément doivent provenir d’une des terminologies de référence suivantes :
+-	TRE_A03-ClasseDocument-CISIS, OID : 1.2.250.1.213.1.1.4.1
+-	TRE_A10-NomenclatureURN, OID : URN
+Les valeurs possibles peuvent être restreintes en fonction du jeu de valeurs correspondant mis à disposition par le projet (exemple : JDV_J57-ClassCode-DMP).
+En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J06-XdsClassCode-CISIS peut être utilisé. {f:category}</t>
   </si>
   <si>
     <t>DocumentReference.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|Group|Device)
+    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrPatient)
 </t>
   </si>
   <si>
-    <t>Who/what is the subject of the document</t>
+    <t>Patient concerné par ce document. La ressource référencée peut être présente sous l’élément DocumentReference.contained ou via le champ identifier.</t>
   </si>
   <si>
     <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
@@ -974,7 +1111,7 @@
 </t>
   </si>
   <si>
-    <t>When this document reference was created</t>
+    <t>Représente la date de création de la ressource DocumentReference dans FHIR</t>
   </si>
   <si>
     <t>When the document reference was created.</t>
@@ -986,11 +1123,11 @@
     <t>DocumentReference.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Device|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|Device|http://interopsante.org/fhir/StructureDefinition/FrPatient|http://interopsante.org/fhir/StructureDefinition/FrRelatedPerson)
 </t>
   </si>
   <si>
-    <t>Who and/or what authored the document</t>
+    <t>Personnes physiques ou morales et/ou les dispositifs auteurs d'un document.</t>
   </si>
   <si>
     <t>Identifies who is responsible for adding the information to the document.</t>
@@ -1002,11 +1139,11 @@
     <t>DocumentReference.authenticator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
 </t>
   </si>
   <si>
-    <t>Who/what authenticated the document</t>
+    <t>Cet attribut représente l’acteur validant le document et prenant la responsabilité du contenu médical de celui-ci. Il peut s’agir de l’auteur du document si celui-ci est une personne et s’il endosse la responsabilité du contenu médical de ses documents. Si l’auteur est un dispositif, cet attribut doit représenter la personne responsable de l’action effectuée par le dispositif.</t>
   </si>
   <si>
     <t>Which person or organization authenticates that this document is valid.</t>
@@ -1086,7 +1223,7 @@
     <t>DocumentReference.description</t>
   </si>
   <si>
-    <t>Human-readable description</t>
+    <t>Commentaire associé au document.</t>
   </si>
   <si>
     <t>Human-readable description of the source document.</t>
@@ -1101,7 +1238,7 @@
     <t>DocumentReference.securityLabel</t>
   </si>
   <si>
-    <t>Document security-tags</t>
+    <t>Contient les informations définissant le niveau de confidentialité d'un document.</t>
   </si>
   <si>
     <t>A set of Security-Tag codes specifying the level of privacy/security of the Document. Note that DocumentReference.meta.security contains the security labels of the "reference" to the document, while DocumentReference.securityLabel contains a snapshot of the security labels on the document the reference refers to.</t>
@@ -1114,13 +1251,8 @@
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+constr-bind-securityLabel:Les codes pour cet élément doivent provenir du ValueSet spécifié par le standard. Lorsqu’aucun code ne correspond au concept recherché, un code provenant de la terminologie de référence TRE_A07-StatusVisibiliteDocument, OID : 1.2.250.1.213.1.1.4.13 peut être utilisé. {f:securityLabel}</t>
   </si>
   <si>
     <t>DocumentReference.content</t>
@@ -1194,7 +1326,7 @@
     <t>DocumentReference.content.attachment.language</t>
   </si>
   <si>
-    <t>Human language of the content (BCP-47)</t>
+    <t>Pour tous les documents produits par les systèmes initiateurs français, le code est "fr-FR'.</t>
   </si>
   <si>
     <t>The human language of the content. The value can be any valid value according to BCP 47.</t>
@@ -1216,7 +1348,7 @@
 </t>
   </si>
   <si>
-    <t>Le document CDA est contenu dans l'élément .data au format base64.</t>
+    <t>Le document est contenu dans l'élément .data au format base64.</t>
   </si>
   <si>
     <t>The actual data of the attachment - a sequence of bytes, base64 encoded.</t>
@@ -1259,7 +1391,7 @@
     <t>DocumentReference.content.attachment.size</t>
   </si>
   <si>
-    <t>Number of bytes of content (if url provided)</t>
+    <t>Représente la taille du document.</t>
   </si>
   <si>
     <t>The number of bytes of data that make up this attachment (before base64 encoding, if that is done).</t>
@@ -1277,7 +1409,7 @@
     <t>DocumentReference.content.attachment.hash</t>
   </si>
   <si>
-    <t>Hash of the data (sha-1, base64ed)</t>
+    <t>Représente le résultat de hachage du document (SHA 1).</t>
   </si>
   <si>
     <t>The calculated hash of the data using SHA-1. Represented using base64.</t>
@@ -1317,7 +1449,7 @@
 </t>
   </si>
   <si>
-    <t>Date attachment was first created</t>
+    <t>Représente la date et l’heure de création du document.</t>
   </si>
   <si>
     <t>The date that the attachment was first created.</t>
@@ -1332,11 +1464,7 @@
     <t>DocumentReference.content.format</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Format/content rules for the document</t>
+    <t>Format technique détaillé du document.</t>
   </si>
   <si>
     <t>An identifier of the document encoding, structure, and template that the document conforms to beyond the base format indicated in the mimeType.</t>
@@ -1345,10 +1473,17 @@
     <t>Note that while IHE mostly issues URNs for format types, not all documents can be identified by a URI.</t>
   </si>
   <si>
-    <t>Document Format Codes.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/formatcodes</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J10-XdsFormatCode-CISIS/FHIR/JDV-J10-XdsFormatCode-CISIS</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+constr-bind-format:Les valeurs possibles pour cet élément doivent provenir d’une des terminologies de référence suivantes :
+- TRE_A06-FormatCodeComplementaire, OID : 1.2.250.1.213.1.1.4.2.282
+- TRE_A11-IheFormatCode, OID : 1.3.6.1.4.1.19376.1.2.3
+- TRE_A09-DICOMuidRegistry, OID : 1.2.840.10008.2.6.1
+- TRE_A10-NomenclatureURN, OID : URN
+Les valeurs possibles peuvent être restreintes en fonction du jeu de valeurs correspondant mis à disposition par le projet (exemple : JDV_J60-FormatCode-DMP).
+En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J10-XdsFormatCode-CISIS peut être utilisé. {f:content/f:format}</t>
   </si>
   <si>
     <t>DocumentReference.context</t>
@@ -1388,7 +1523,7 @@
     <t>DocumentReference.context.event</t>
   </si>
   <si>
-    <t>Main clinical acts documented</t>
+    <t>Représente les actes et les pathologies en rapport avec le document.</t>
   </si>
   <si>
     <t>This list of codes represents the main clinical acts, such as a colonoscopy or an appendectomy, being documented. In some cases, the event is inherent in the type Code, such as a "History and Physical Report" in which the procedure being documented is necessarily a "History and Physical" act.</t>
@@ -1401,6 +1536,13 @@
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+constr-bind-context-event:Nomenclatures utilisées :
+- CCAM pour les actes médicaux (OID="1.2.250.1.213.2.5");
+- CIM-10 pour les diagnostics de pathologie (OID="2.16.840.1.113883.6.3").
+- TRE_A00-ProducteurDocNonPS pour les documents d'expression personnelle du patient. {f:context/f:event}</t>
   </si>
   <si>
     <t>DocumentReference.context.period</t>
@@ -1427,7 +1569,7 @@
     <t>DocumentReference.context.facilityType</t>
   </si>
   <si>
-    <t>Kind of facility where patient was seen</t>
+    <t>Secteur d'activité lié à la prise en charge de la personne, en lien avec le document produit.</t>
   </si>
   <si>
     <t>The kind of facility where the patient was seen.</t>
@@ -1436,16 +1578,20 @@
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
-    <t>XDS Facility Type.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J02-XdsHealthcareFacilityTypeCode-CISIS/FHIR/JDV-J02-XdsHealthcareFacilityTypeCode-CISIS</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+constr-bind-ProducteurDoc-simplified:L’utilisation de cette nomenclature est recommandée mais non obligatoire (prefered) :
+-	TRE_R02-SecteurActivite, OID : 1.2.250.1.71.4.2.4 (lorsque l’auteur du document est un professionnel ou un équipement sous sa responsabilité)
+Les valeurs possibles peuvent être restreintes en fonction du jeu de valeurs correspondant mis à disposition par le projet (exemple : JDV_J61-HealthcareFacilityTypeCode-DMP).
+En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J02-XdsHealthcareFacilityTypeCode-CISIS peut être utilisé. {f:context/f:practiceSetting or f:context/f:facilityType}</t>
   </si>
   <si>
     <t>DocumentReference.context.practiceSetting</t>
   </si>
   <si>
-    <t>Additional details about where the content was created (e.g. clinical specialty)</t>
+    <t>Cadre d’exercice de l’acte qui a engendré la création du document.</t>
   </si>
   <si>
     <t>This property may convey specifics about the practice setting where the content was created, often reflecting the clinical specialty.</t>
@@ -1457,20 +1603,13 @@
     <t>This is an important piece of metadata that providers often rely upon to quickly sort and/or filter out to find specific content.</t>
   </si>
   <si>
-    <t>Additional details about where the content was created (e.g. clinical specialty).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J04-XdsPracticeSettingCode-CISIS/FHIR/JDV-J04-XdsPracticeSettingCode-CISIS</t>
   </si>
   <si>
     <t>DocumentReference.context.sourcePatientInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
-</t>
-  </si>
-  <si>
-    <t>Patient demographics from source</t>
+    <t>Référence vers la ressource Patient titulaire du dossier.</t>
   </si>
   <si>
     <t>The Patient Information as known when the document was published. May be a reference to a version specific, or contained.</t>
@@ -1826,7 +1965,9 @@
       <c r="A26" t="s" s="2">
         <v>10</v>
       </c>
-      <c r="B26" s="2"/>
+      <c r="B26" t="s" s="2">
+        <v>232</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
@@ -1871,7 +2012,7 @@
         <v>20</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33">
@@ -1907,7 +2048,7 @@
         <v>28</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="38">
@@ -1915,7 +2056,7 @@
         <v>30</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="39">
@@ -1941,7 +2082,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK103"/>
+  <dimension ref="A1:AK111"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.625" customWidth="true" bestFit="true"/>
@@ -1960,14 +2101,14 @@
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.73046875" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="35.69140625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="10.53125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="168.19140625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="57.0" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="120.0625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="10.26171875" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -7013,10 +7154,10 @@
         <v>229</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -7098,7 +7239,7 @@
         <v>36</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>37</v>
@@ -7118,10 +7259,10 @@
         <v>229</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7223,10 +7364,10 @@
         <v>229</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -7326,10 +7467,10 @@
         <v>229</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -7346,23 +7487,21 @@
         <v>36</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>62</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" s="2"/>
       <c r="Q52" t="s" s="2">
         <v>36</v>
@@ -7411,7 +7550,7 @@
         <v>36</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>37</v>
@@ -7420,10 +7559,10 @@
         <v>44</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>57</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53">
@@ -7431,21 +7570,21 @@
         <v>229</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" t="s" s="2">
         <v>37</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>36</v>
@@ -7457,16 +7596,16 @@
         <v>36</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="P53" s="2"/>
       <c r="Q53" t="s" s="2">
@@ -7492,43 +7631,43 @@
         <v>36</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AA53" t="s" s="2">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="AB53" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="AD53" t="s" s="2">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="AE53" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54">
@@ -7536,14 +7675,14 @@
         <v>229</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" t="s" s="2">
@@ -7553,25 +7692,25 @@
         <v>44</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>36</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P54" s="2"/>
       <c r="Q54" t="s" s="2">
@@ -7621,7 +7760,7 @@
         <v>36</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>37</v>
@@ -7641,21 +7780,21 @@
         <v>229</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
-        <v>247</v>
+        <v>36</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" t="s" s="2">
         <v>37</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>36</v>
@@ -7664,19 +7803,19 @@
         <v>36</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>219</v>
+        <v>86</v>
       </c>
       <c r="M55" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O55" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="P55" s="2"/>
       <c r="Q55" t="s" s="2">
@@ -7726,19 +7865,19 @@
         <v>36</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>36</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56">
@@ -7746,21 +7885,21 @@
         <v>229</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" t="s" s="2">
         <v>37</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>36</v>
@@ -7769,19 +7908,19 @@
         <v>36</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>109</v>
+        <v>251</v>
       </c>
       <c r="N56" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="O56" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="P56" s="2"/>
       <c r="Q56" t="s" s="2">
@@ -7819,16 +7958,16 @@
         <v>36</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="AD56" t="s" s="2">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="AE56" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>254</v>
@@ -7837,13 +7976,13 @@
         <v>37</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57">
@@ -7858,7 +7997,7 @@
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" t="s" s="2">
@@ -7871,26 +8010,24 @@
         <v>36</v>
       </c>
       <c r="J57" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K57" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="K57" t="s" s="2">
-        <v>36</v>
-      </c>
       <c r="L57" t="s" s="2">
-        <v>108</v>
+        <v>256</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="P57" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="P57" s="2"/>
       <c r="Q57" t="s" s="2">
         <v>36</v>
       </c>
@@ -7926,19 +8063,19 @@
         <v>36</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="AD57" t="s" s="2">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="AE57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>37</v>
@@ -7950,7 +8087,7 @@
         <v>56</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58">
@@ -7958,10 +8095,10 @@
         <v>229</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -7972,7 +8109,7 @@
         <v>37</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>36</v>
@@ -7984,20 +8121,18 @@
         <v>45</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>74</v>
+        <v>262</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="P58" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="P58" s="2"/>
       <c r="Q58" t="s" s="2">
         <v>36</v>
       </c>
@@ -8021,13 +8156,13 @@
         <v>36</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>36</v>
+        <v>266</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>36</v>
+        <v>267</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>36</v>
+        <v>268</v>
       </c>
       <c r="AB58" t="s" s="2">
         <v>36</v>
@@ -8045,13 +8180,13 @@
         <v>36</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>56</v>
@@ -8065,10 +8200,10 @@
         <v>229</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -8091,15 +8226,17 @@
         <v>45</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>74</v>
+        <v>262</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P59" s="2"/>
       <c r="Q59" t="s" s="2">
         <v>36</v>
@@ -8124,13 +8261,13 @@
         <v>36</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>36</v>
+        <v>274</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>36</v>
+        <v>275</v>
       </c>
       <c r="AA59" t="s" s="2">
-        <v>36</v>
+        <v>276</v>
       </c>
       <c r="AB59" t="s" s="2">
         <v>36</v>
@@ -8148,7 +8285,7 @@
         <v>36</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>37</v>
@@ -8168,10 +8305,10 @@
         <v>229</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -8179,7 +8316,7 @@
       </c>
       <c r="F60" s="2"/>
       <c r="G60" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>44</v>
@@ -8194,16 +8331,16 @@
         <v>45</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>268</v>
+        <v>60</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>269</v>
+        <v>61</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>270</v>
+        <v>62</v>
       </c>
       <c r="P60" s="2"/>
       <c r="Q60" t="s" s="2">
@@ -8229,13 +8366,13 @@
         <v>36</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>271</v>
+        <v>36</v>
       </c>
       <c r="AA60" t="s" s="2">
-        <v>272</v>
+        <v>36</v>
       </c>
       <c r="AB60" t="s" s="2">
         <v>36</v>
@@ -8253,10 +8390,10 @@
         <v>36</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>267</v>
+        <v>63</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>44</v>
@@ -8273,10 +8410,10 @@
         <v>229</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -8296,19 +8433,19 @@
         <v>36</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>65</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>274</v>
+        <v>66</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>275</v>
+        <v>67</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>276</v>
+        <v>68</v>
       </c>
       <c r="P61" s="2"/>
       <c r="Q61" t="s" s="2">
@@ -8334,13 +8471,13 @@
         <v>36</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>277</v>
+        <v>70</v>
       </c>
       <c r="AA61" t="s" s="2">
-        <v>278</v>
+        <v>71</v>
       </c>
       <c r="AB61" t="s" s="2">
         <v>36</v>
@@ -8358,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>273</v>
+        <v>72</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>37</v>
@@ -8378,14 +8515,14 @@
         <v>229</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
-        <v>36</v>
+        <v>281</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" t="s" s="2">
@@ -8401,19 +8538,19 @@
         <v>36</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="P62" s="2"/>
       <c r="Q62" t="s" s="2">
@@ -8439,13 +8576,13 @@
         <v>36</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>284</v>
+        <v>36</v>
       </c>
       <c r="AA62" t="s" s="2">
-        <v>285</v>
+        <v>36</v>
       </c>
       <c r="AB62" t="s" s="2">
         <v>36</v>
@@ -8463,7 +8600,7 @@
         <v>36</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>37</v>
@@ -8483,14 +8620,14 @@
         <v>229</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" t="s" s="2">
@@ -8506,19 +8643,19 @@
         <v>36</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>280</v>
+        <v>219</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" t="s" s="2">
@@ -8544,31 +8681,31 @@
         <v>36</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>291</v>
+        <v>36</v>
       </c>
       <c r="Z63" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AG63" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>37</v>
@@ -8577,10 +8714,10 @@
         <v>38</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>57</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64">
@@ -8588,21 +8725,21 @@
         <v>229</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" t="s" s="2">
         <v>37</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>36</v>
@@ -8611,19 +8748,19 @@
         <v>36</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>295</v>
+        <v>108</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>296</v>
+        <v>109</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>298</v>
+        <v>111</v>
       </c>
       <c r="P64" s="2"/>
       <c r="Q64" t="s" s="2">
@@ -8661,31 +8798,31 @@
         <v>36</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="AD64" t="s" s="2">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="AE64" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>299</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65">
@@ -8693,44 +8830,46 @@
         <v>229</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
-        <v>301</v>
+        <v>107</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" t="s" s="2">
         <v>37</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="P65" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>121</v>
+      </c>
       <c r="Q65" t="s" s="2">
         <v>36</v>
       </c>
@@ -8766,31 +8905,31 @@
         <v>36</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="AD65" t="s" s="2">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="AE65" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66">
@@ -8798,10 +8937,10 @@
         <v>229</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -8812,10 +8951,10 @@
         <v>37</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>36</v>
@@ -8824,18 +8963,20 @@
         <v>45</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>306</v>
+        <v>74</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="P66" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="Q66" t="s" s="2">
         <v>36</v>
       </c>
@@ -8883,19 +9024,19 @@
         <v>36</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>299</v>
+        <v>57</v>
       </c>
     </row>
     <row r="67">
@@ -8903,10 +9044,10 @@
         <v>229</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -8917,29 +9058,27 @@
         <v>37</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>36</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>311</v>
+        <v>74</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" s="2"/>
       <c r="Q67" t="s" s="2">
         <v>36</v>
@@ -8988,19 +9127,19 @@
         <v>36</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>299</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68">
@@ -9008,10 +9147,10 @@
         <v>229</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -9019,31 +9158,31 @@
       </c>
       <c r="F68" s="2"/>
       <c r="G68" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>44</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>316</v>
+        <v>65</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="P68" s="2"/>
       <c r="Q68" t="s" s="2">
@@ -9054,7 +9193,7 @@
         <v>36</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>36</v>
+        <v>312</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>36</v>
@@ -9069,13 +9208,13 @@
         <v>36</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>36</v>
+        <v>313</v>
       </c>
       <c r="AA68" t="s" s="2">
-        <v>36</v>
+        <v>314</v>
       </c>
       <c r="AB68" t="s" s="2">
         <v>36</v>
@@ -9093,10 +9232,10 @@
         <v>36</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>44</v>
@@ -9105,7 +9244,7 @@
         <v>56</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>299</v>
+        <v>57</v>
       </c>
     </row>
     <row r="69">
@@ -9113,10 +9252,10 @@
         <v>229</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -9127,7 +9266,7 @@
         <v>37</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>36</v>
@@ -9139,16 +9278,16 @@
         <v>45</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="P69" s="2"/>
       <c r="Q69" t="s" s="2">
@@ -9174,13 +9313,13 @@
         <v>36</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>36</v>
+        <v>319</v>
       </c>
       <c r="AA69" t="s" s="2">
-        <v>36</v>
+        <v>320</v>
       </c>
       <c r="AB69" t="s" s="2">
         <v>36</v>
@@ -9198,13 +9337,13 @@
         <v>36</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>56</v>
@@ -9218,10 +9357,10 @@
         <v>229</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -9235,24 +9374,26 @@
         <v>44</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J70" t="s" s="2">
         <v>36</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>102</v>
+        <v>322</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>103</v>
+        <v>323</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="P70" s="2"/>
       <c r="Q70" t="s" s="2">
         <v>36</v>
@@ -9277,13 +9418,11 @@
         <v>36</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>36</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="Z70" s="2"/>
       <c r="AA70" t="s" s="2">
-        <v>36</v>
+        <v>326</v>
       </c>
       <c r="AB70" t="s" s="2">
         <v>36</v>
@@ -9301,7 +9440,7 @@
         <v>36</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>105</v>
+        <v>321</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>37</v>
@@ -9310,10 +9449,10 @@
         <v>44</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>36</v>
+        <v>327</v>
       </c>
     </row>
     <row r="71">
@@ -9321,14 +9460,14 @@
         <v>229</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
-        <v>107</v>
+        <v>329</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" t="s" s="2">
@@ -9338,25 +9477,25 @@
         <v>38</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J71" t="s" s="2">
         <v>36</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>108</v>
+        <v>322</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>109</v>
+        <v>330</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>110</v>
+        <v>331</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>111</v>
+        <v>332</v>
       </c>
       <c r="P71" s="2"/>
       <c r="Q71" t="s" s="2">
@@ -9382,31 +9521,29 @@
         <v>36</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>36</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="Z71" s="2"/>
       <c r="AA71" t="s" s="2">
-        <v>36</v>
+        <v>333</v>
       </c>
       <c r="AB71" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="AD71" t="s" s="2">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="AE71" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>115</v>
+        <v>328</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>37</v>
@@ -9418,7 +9555,7 @@
         <v>56</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>116</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72">
@@ -9426,46 +9563,44 @@
         <v>229</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
-        <v>118</v>
+        <v>36</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" t="s" s="2">
         <v>37</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="K72" t="s" s="2">
         <v>45</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>108</v>
+        <v>336</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>119</v>
+        <v>337</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>120</v>
+        <v>338</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="P72" s="2"/>
       <c r="Q72" t="s" s="2">
         <v>36</v>
       </c>
@@ -9513,19 +9648,19 @@
         <v>36</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>122</v>
+        <v>335</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>116</v>
+        <v>340</v>
       </c>
     </row>
     <row r="73">
@@ -9533,24 +9668,24 @@
         <v>229</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
-        <v>36</v>
+        <v>342</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>44</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J73" t="s" s="2">
         <v>36</v>
@@ -9559,16 +9694,16 @@
         <v>45</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="P73" s="2"/>
       <c r="Q73" t="s" s="2">
@@ -9594,13 +9729,13 @@
         <v>36</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>331</v>
+        <v>36</v>
       </c>
       <c r="AA73" t="s" s="2">
-        <v>332</v>
+        <v>36</v>
       </c>
       <c r="AB73" t="s" s="2">
         <v>36</v>
@@ -9618,10 +9753,10 @@
         <v>36</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>44</v>
@@ -9638,10 +9773,10 @@
         <v>229</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -9649,13 +9784,13 @@
       </c>
       <c r="F74" s="2"/>
       <c r="G74" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>36</v>
@@ -9664,16 +9799,16 @@
         <v>45</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>298</v>
+        <v>350</v>
       </c>
       <c r="P74" s="2"/>
       <c r="Q74" t="s" s="2">
@@ -9723,19 +9858,19 @@
         <v>36</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>299</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75">
@@ -9743,10 +9878,10 @@
         <v>229</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -9760,29 +9895,27 @@
         <v>44</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J75" t="s" s="2">
         <v>36</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>102</v>
+        <v>352</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="P75" s="2"/>
       <c r="Q75" t="s" s="2">
         <v>36</v>
       </c>
@@ -9830,7 +9963,7 @@
         <v>36</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>37</v>
@@ -9842,7 +9975,7 @@
         <v>56</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>57</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76">
@@ -9850,10 +9983,10 @@
         <v>229</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -9864,7 +9997,7 @@
         <v>37</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>36</v>
@@ -9873,23 +10006,21 @@
         <v>36</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>280</v>
+        <v>357</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="P76" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="P76" s="2"/>
       <c r="Q76" t="s" s="2">
         <v>36</v>
       </c>
@@ -9913,13 +10044,13 @@
         <v>36</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>347</v>
+        <v>36</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>348</v>
+        <v>36</v>
       </c>
       <c r="AA76" t="s" s="2">
-        <v>349</v>
+        <v>36</v>
       </c>
       <c r="AB76" t="s" s="2">
         <v>36</v>
@@ -9937,19 +10068,19 @@
         <v>36</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>57</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77">
@@ -9957,10 +10088,10 @@
         <v>229</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -9968,13 +10099,13 @@
       </c>
       <c r="F77" s="2"/>
       <c r="G77" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>36</v>
@@ -9986,12 +10117,14 @@
         <v>97</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="P77" s="2"/>
       <c r="Q77" t="s" s="2">
         <v>36</v>
@@ -10040,10 +10173,10 @@
         <v>36</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>38</v>
@@ -10060,10 +10193,10 @@
         <v>229</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -10163,10 +10296,10 @@
         <v>229</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -10268,10 +10401,10 @@
         <v>229</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -10375,10 +10508,10 @@
         <v>229</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -10401,16 +10534,16 @@
         <v>45</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>357</v>
+        <v>65</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="P81" s="2"/>
       <c r="Q81" t="s" s="2">
@@ -10436,13 +10569,13 @@
         <v>36</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>36</v>
+        <v>372</v>
       </c>
       <c r="AA81" t="s" s="2">
-        <v>36</v>
+        <v>373</v>
       </c>
       <c r="AB81" t="s" s="2">
         <v>36</v>
@@ -10460,7 +10593,7 @@
         <v>36</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>44</v>
@@ -10472,7 +10605,7 @@
         <v>56</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>361</v>
+        <v>57</v>
       </c>
     </row>
     <row r="82">
@@ -10480,10 +10613,10 @@
         <v>229</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -10491,7 +10624,7 @@
       </c>
       <c r="F82" s="2"/>
       <c r="G82" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>44</v>
@@ -10503,18 +10636,20 @@
         <v>36</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>102</v>
+        <v>375</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>103</v>
+        <v>376</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P82" s="2"/>
       <c r="Q82" t="s" s="2">
         <v>36</v>
@@ -10563,19 +10698,19 @@
         <v>36</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>105</v>
+        <v>374</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>44</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>36</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83">
@@ -10583,44 +10718,46 @@
         <v>229</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" t="s" s="2">
         <v>37</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>36</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>109</v>
+        <v>379</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>110</v>
+        <v>380</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="P83" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="Q83" t="s" s="2">
         <v>36</v>
       </c>
@@ -10656,31 +10793,31 @@
         <v>36</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="AD83" t="s" s="2">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="AE83" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>115</v>
+        <v>378</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="84">
@@ -10688,10 +10825,10 @@
         <v>229</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -10702,7 +10839,7 @@
         <v>37</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>36</v>
@@ -10714,19 +10851,19 @@
         <v>45</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>65</v>
+        <v>322</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>126</v>
+        <v>386</v>
       </c>
       <c r="P84" t="s" s="2">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="Q84" t="s" s="2">
         <v>36</v>
@@ -10739,7 +10876,7 @@
         <v>36</v>
       </c>
       <c r="U84" t="s" s="2">
-        <v>368</v>
+        <v>36</v>
       </c>
       <c r="V84" t="s" s="2">
         <v>36</v>
@@ -10751,13 +10888,13 @@
         <v>36</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>369</v>
+        <v>267</v>
       </c>
       <c r="AA84" t="s" s="2">
-        <v>370</v>
+        <v>268</v>
       </c>
       <c r="AB84" t="s" s="2">
         <v>36</v>
@@ -10775,19 +10912,19 @@
         <v>36</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>57</v>
+        <v>388</v>
       </c>
     </row>
     <row r="85">
@@ -10795,10 +10932,10 @@
         <v>229</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -10806,13 +10943,13 @@
       </c>
       <c r="F85" s="2"/>
       <c r="G85" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J85" t="s" s="2">
         <v>36</v>
@@ -10821,20 +10958,16 @@
         <v>45</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="P85" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="O85" s="2"/>
+      <c r="P85" s="2"/>
       <c r="Q85" t="s" s="2">
         <v>36</v>
       </c>
@@ -10846,7 +10979,7 @@
         <v>36</v>
       </c>
       <c r="U85" t="s" s="2">
-        <v>376</v>
+        <v>36</v>
       </c>
       <c r="V85" t="s" s="2">
         <v>36</v>
@@ -10858,13 +10991,13 @@
         <v>36</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AA85" t="s" s="2">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="AB85" t="s" s="2">
         <v>36</v>
@@ -10882,13 +11015,13 @@
         <v>36</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>56</v>
@@ -10902,10 +11035,10 @@
         <v>229</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -10913,7 +11046,7 @@
       </c>
       <c r="F86" s="2"/>
       <c r="G86" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>44</v>
@@ -10928,20 +11061,16 @@
         <v>36</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>379</v>
+        <v>102</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>380</v>
+        <v>103</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="P86" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="O86" s="2"/>
+      <c r="P86" s="2"/>
       <c r="Q86" t="s" s="2">
         <v>36</v>
       </c>
@@ -10989,7 +11118,7 @@
         <v>36</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>384</v>
+        <v>105</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>37</v>
@@ -10998,10 +11127,10 @@
         <v>44</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>57</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87">
@@ -11009,21 +11138,21 @@
         <v>229</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" t="s" s="2">
         <v>37</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>36</v>
@@ -11032,23 +11161,21 @@
         <v>36</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>386</v>
+        <v>108</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>387</v>
+        <v>109</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>388</v>
+        <v>110</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="P87" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="P87" s="2"/>
       <c r="Q87" t="s" s="2">
         <v>36</v>
       </c>
@@ -11060,7 +11187,7 @@
         <v>36</v>
       </c>
       <c r="U87" t="s" s="2">
-        <v>391</v>
+        <v>36</v>
       </c>
       <c r="V87" t="s" s="2">
         <v>36</v>
@@ -11084,31 +11211,31 @@
         <v>36</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="AD87" t="s" s="2">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="AE87" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>392</v>
+        <v>115</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="88">
@@ -11116,45 +11243,45 @@
         <v>229</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" t="s" s="2">
         <v>37</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K88" t="s" s="2">
         <v>45</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>394</v>
+        <v>119</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>395</v>
+        <v>120</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>396</v>
+        <v>111</v>
       </c>
       <c r="P88" t="s" s="2">
-        <v>397</v>
+        <v>121</v>
       </c>
       <c r="Q88" t="s" s="2">
         <v>36</v>
@@ -11203,19 +11330,19 @@
         <v>36</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>398</v>
+        <v>122</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="89">
@@ -11223,10 +11350,10 @@
         <v>229</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -11234,7 +11361,7 @@
       </c>
       <c r="F89" s="2"/>
       <c r="G89" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>44</v>
@@ -11249,20 +11376,18 @@
         <v>45</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="P89" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="P89" s="2"/>
       <c r="Q89" t="s" s="2">
         <v>36</v>
       </c>
@@ -11310,10 +11435,10 @@
         <v>36</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>44</v>
@@ -11322,7 +11447,7 @@
         <v>56</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>57</v>
+        <v>400</v>
       </c>
     </row>
     <row r="90">
@@ -11330,10 +11455,10 @@
         <v>229</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -11353,23 +11478,19 @@
         <v>36</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>102</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>406</v>
+        <v>103</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="P90" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="O90" s="2"/>
+      <c r="P90" s="2"/>
       <c r="Q90" t="s" s="2">
         <v>36</v>
       </c>
@@ -11381,7 +11502,7 @@
         <v>36</v>
       </c>
       <c r="U90" t="s" s="2">
-        <v>409</v>
+        <v>36</v>
       </c>
       <c r="V90" t="s" s="2">
         <v>36</v>
@@ -11417,7 +11538,7 @@
         <v>36</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>410</v>
+        <v>105</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>37</v>
@@ -11426,10 +11547,10 @@
         <v>44</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>57</v>
+        <v>36</v>
       </c>
     </row>
     <row r="91">
@@ -11437,21 +11558,21 @@
         <v>229</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="F91" s="2"/>
       <c r="G91" t="s" s="2">
         <v>37</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>36</v>
@@ -11460,21 +11581,21 @@
         <v>36</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>412</v>
+        <v>108</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>413</v>
+        <v>109</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O91" s="2"/>
-      <c r="P91" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="P91" s="2"/>
       <c r="Q91" t="s" s="2">
         <v>36</v>
       </c>
@@ -11510,31 +11631,31 @@
         <v>36</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="AD91" t="s" s="2">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="AE91" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>416</v>
+        <v>115</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92">
@@ -11542,10 +11663,10 @@
         <v>229</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -11553,7 +11674,7 @@
       </c>
       <c r="F92" s="2"/>
       <c r="G92" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>44</v>
@@ -11568,18 +11689,20 @@
         <v>45</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>418</v>
+        <v>65</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="P92" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="Q92" t="s" s="2">
         <v>36</v>
       </c>
@@ -11591,7 +11714,7 @@
         <v>36</v>
       </c>
       <c r="U92" t="s" s="2">
-        <v>36</v>
+        <v>407</v>
       </c>
       <c r="V92" t="s" s="2">
         <v>36</v>
@@ -11603,13 +11726,13 @@
         <v>36</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="AA92" t="s" s="2">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="AB92" t="s" s="2">
         <v>36</v>
@@ -11627,7 +11750,7 @@
         <v>36</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>37</v>
@@ -11647,10 +11770,10 @@
         <v>229</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -11664,7 +11787,7 @@
         <v>44</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J93" t="s" s="2">
         <v>36</v>
@@ -11673,18 +11796,20 @@
         <v>45</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="P93" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="Q93" t="s" s="2">
         <v>36</v>
       </c>
@@ -11696,7 +11821,7 @@
         <v>36</v>
       </c>
       <c r="U93" t="s" s="2">
-        <v>36</v>
+        <v>415</v>
       </c>
       <c r="V93" t="s" s="2">
         <v>36</v>
@@ -11708,13 +11833,13 @@
         <v>36</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AA93" t="s" s="2">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="AB93" t="s" s="2">
         <v>36</v>
@@ -11732,7 +11857,7 @@
         <v>36</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>37</v>
@@ -11752,10 +11877,10 @@
         <v>229</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -11763,7 +11888,7 @@
       </c>
       <c r="F94" s="2"/>
       <c r="G94" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>44</v>
@@ -11778,16 +11903,20 @@
         <v>36</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>102</v>
+        <v>418</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>103</v>
+        <v>419</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O94" s="2"/>
-      <c r="P94" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="Q94" t="s" s="2">
         <v>36</v>
       </c>
@@ -11835,7 +11964,7 @@
         <v>36</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>105</v>
+        <v>423</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>37</v>
@@ -11844,10 +11973,10 @@
         <v>44</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>36</v>
+        <v>57</v>
       </c>
     </row>
     <row r="95">
@@ -11855,21 +11984,21 @@
         <v>229</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" t="s" s="2">
         <v>37</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>36</v>
@@ -11878,21 +12007,23 @@
         <v>36</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>108</v>
+        <v>425</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>109</v>
+        <v>426</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>110</v>
+        <v>427</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="P95" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="Q95" t="s" s="2">
         <v>36</v>
       </c>
@@ -11904,7 +12035,7 @@
         <v>36</v>
       </c>
       <c r="U95" t="s" s="2">
-        <v>36</v>
+        <v>430</v>
       </c>
       <c r="V95" t="s" s="2">
         <v>36</v>
@@ -11928,31 +12059,31 @@
         <v>36</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="AD95" t="s" s="2">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="AE95" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>115</v>
+        <v>431</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="96">
@@ -11960,45 +12091,45 @@
         <v>229</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
-        <v>118</v>
+        <v>36</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" t="s" s="2">
         <v>37</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="K96" t="s" s="2">
         <v>45</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>119</v>
+        <v>433</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>120</v>
+        <v>434</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>111</v>
+        <v>435</v>
       </c>
       <c r="P96" t="s" s="2">
-        <v>121</v>
+        <v>436</v>
       </c>
       <c r="Q96" t="s" s="2">
         <v>36</v>
@@ -12047,19 +12178,19 @@
         <v>36</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>122</v>
+        <v>437</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="97">
@@ -12067,10 +12198,10 @@
         <v>229</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -12081,7 +12212,7 @@
         <v>37</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>36</v>
@@ -12090,21 +12221,23 @@
         <v>36</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="P97" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="Q97" t="s" s="2">
         <v>36</v>
       </c>
@@ -12152,19 +12285,19 @@
         <v>36</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>299</v>
+        <v>57</v>
       </c>
     </row>
     <row r="98">
@@ -12172,10 +12305,10 @@
         <v>229</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -12183,10 +12316,10 @@
       </c>
       <c r="F98" s="2"/>
       <c r="G98" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>36</v>
@@ -12195,21 +12328,23 @@
         <v>36</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>280</v>
+        <v>102</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="P98" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="Q98" t="s" s="2">
         <v>36</v>
       </c>
@@ -12221,7 +12356,7 @@
         <v>36</v>
       </c>
       <c r="U98" t="s" s="2">
-        <v>36</v>
+        <v>448</v>
       </c>
       <c r="V98" t="s" s="2">
         <v>36</v>
@@ -12233,13 +12368,13 @@
         <v>36</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>291</v>
+        <v>36</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>439</v>
+        <v>36</v>
       </c>
       <c r="AA98" t="s" s="2">
-        <v>440</v>
+        <v>36</v>
       </c>
       <c r="AB98" t="s" s="2">
         <v>36</v>
@@ -12257,13 +12392,13 @@
         <v>36</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>56</v>
@@ -12277,10 +12412,10 @@
         <v>229</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -12294,7 +12429,7 @@
         <v>44</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>36</v>
@@ -12303,18 +12438,18 @@
         <v>45</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="P99" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="Q99" t="s" s="2">
         <v>36</v>
       </c>
@@ -12362,7 +12497,7 @@
         <v>36</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>37</v>
@@ -12374,7 +12509,7 @@
         <v>56</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>446</v>
+        <v>57</v>
       </c>
     </row>
     <row r="100">
@@ -12382,10 +12517,10 @@
         <v>229</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -12399,25 +12534,25 @@
         <v>44</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J100" t="s" s="2">
         <v>36</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="P100" s="2"/>
       <c r="Q100" t="s" s="2">
@@ -12443,13 +12578,11 @@
         <v>36</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="Z100" s="2"/>
       <c r="AA100" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="AB100" t="s" s="2">
         <v>36</v>
@@ -12467,7 +12600,7 @@
         <v>36</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>37</v>
@@ -12479,7 +12612,7 @@
         <v>56</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>57</v>
+        <v>461</v>
       </c>
     </row>
     <row r="101">
@@ -12487,10 +12620,10 @@
         <v>229</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -12504,29 +12637,27 @@
         <v>44</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J101" t="s" s="2">
         <v>36</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>280</v>
+        <v>97</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="P101" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="P101" s="2"/>
       <c r="Q101" t="s" s="2">
         <v>36</v>
       </c>
@@ -12550,13 +12681,13 @@
         <v>36</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>291</v>
+        <v>36</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>458</v>
+        <v>36</v>
       </c>
       <c r="AA101" t="s" s="2">
-        <v>459</v>
+        <v>36</v>
       </c>
       <c r="AB101" t="s" s="2">
         <v>36</v>
@@ -12574,7 +12705,7 @@
         <v>36</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>37</v>
@@ -12594,10 +12725,10 @@
         <v>229</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -12620,17 +12751,15 @@
         <v>36</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>461</v>
+        <v>102</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>462</v>
+        <v>103</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="O102" s="2"/>
       <c r="P102" s="2"/>
       <c r="Q102" t="s" s="2">
         <v>36</v>
@@ -12679,7 +12808,7 @@
         <v>36</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>460</v>
+        <v>105</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>37</v>
@@ -12688,10 +12817,10 @@
         <v>44</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>299</v>
+        <v>36</v>
       </c>
     </row>
     <row r="103">
@@ -12699,14 +12828,14 @@
         <v>229</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" t="s" s="2">
@@ -12725,16 +12854,16 @@
         <v>36</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>465</v>
+        <v>108</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>466</v>
+        <v>109</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>467</v>
+        <v>110</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>468</v>
+        <v>111</v>
       </c>
       <c r="P103" s="2"/>
       <c r="Q103" t="s" s="2">
@@ -12772,19 +12901,19 @@
         <v>36</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="AD103" t="s" s="2">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="AE103" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>464</v>
+        <v>115</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>37</v>
@@ -12796,7 +12925,847 @@
         <v>56</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>299</v>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="D104" s="2"/>
+      <c r="E104" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="F104" s="2"/>
+      <c r="G104" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="P104" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="Q104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="R104" s="2"/>
+      <c r="S104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="D105" s="2"/>
+      <c r="E105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F105" s="2"/>
+      <c r="G105" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="P105" s="2"/>
+      <c r="Q105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="R105" s="2"/>
+      <c r="S105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="D106" s="2"/>
+      <c r="E106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F106" s="2"/>
+      <c r="G106" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="P106" s="2"/>
+      <c r="Q106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="R106" s="2"/>
+      <c r="S106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="D107" s="2"/>
+      <c r="E107" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F107" s="2"/>
+      <c r="G107" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="P107" s="2"/>
+      <c r="Q107" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="R107" s="2"/>
+      <c r="S107" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="D108" s="2"/>
+      <c r="E108" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F108" s="2"/>
+      <c r="G108" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="P108" s="2"/>
+      <c r="Q108" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="R108" s="2"/>
+      <c r="S108" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="Z108" s="2"/>
+      <c r="AA108" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="C109" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="D109" s="2"/>
+      <c r="E109" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F109" s="2"/>
+      <c r="G109" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="Q109" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="R109" s="2"/>
+      <c r="S109" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="Z109" s="2"/>
+      <c r="AA109" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="D110" s="2"/>
+      <c r="E110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F110" s="2"/>
+      <c r="G110" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="P110" s="2"/>
+      <c r="Q110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="R110" s="2"/>
+      <c r="S110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="D111" s="2"/>
+      <c r="E111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F111" s="2"/>
+      <c r="G111" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="P111" s="2"/>
+      <c r="Q111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="R111" s="2"/>
+      <c r="S111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>340</v>
       </c>
     </row>
   </sheetData>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-18T14:13:30+00:00</t>
+    <t>2023-09-18T16:20:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-18T16:20:24+00:00</t>
+    <t>2023-09-20T09:28:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T09:28:33+00:00</t>
+    <t>2023-09-20T10:55:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T15:02:23+00:00</t>
+    <t>2023-09-21T09:50:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-21T09:50:54+00:00</t>
+    <t>2023-09-21T10:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-21T10:44:28+00:00</t>
+    <t>2023-09-21T12:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-21T12:08:39+00:00</t>
+    <t>2023-09-21T12:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5045" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3731" uniqueCount="508">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-21T12:39:02+00:00</t>
+    <t>2023-09-21T14:50:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -618,11 +618,11 @@
     <t>DocumentReference.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrPatient)
+    <t xml:space="preserve">Reference(Patient)
 </t>
   </si>
   <si>
-    <t>Patient concerné par ce document. La ressource référencée peut être présente sous l’élément DocumentReference.contained ou via le champ identifier.</t>
+    <t>Who/what is the subject of the document</t>
   </si>
   <si>
     <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
@@ -654,7 +654,7 @@
     <t>DocumentReference.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|Device|http://interopsante.org/fhir/StructureDefinition/FrPatient|http://interopsante.org/fhir/StructureDefinition/FrRelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Device|Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -670,7 +670,7 @@
     <t>DocumentReference.authenticator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization)
 </t>
   </si>
   <si>
@@ -1168,6 +1168,10 @@
     <t>DocumentReference.context.sourcePatientInfo</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrPatient)
+</t>
+  </si>
+  <si>
     <t>Référence vers la ressource Patient titulaire du dossier.</t>
   </si>
   <si>
@@ -1227,33 +1231,6 @@
     <t>Bundle.meta</t>
   </si>
   <si>
-    <t>Bundle.meta.id</t>
-  </si>
-  <si>
-    <t>Bundle.meta.extension</t>
-  </si>
-  <si>
-    <t>Bundle.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>Bundle.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>Bundle.meta.source</t>
-  </si>
-  <si>
-    <t>Bundle.meta.profile</t>
-  </si>
-  <si>
-    <t>Bundle.meta.security</t>
-  </si>
-  <si>
-    <t>Bundle.meta.tag</t>
-  </si>
-  <si>
     <t>Bundle.implicitRules</t>
   </si>
   <si>
@@ -1282,9 +1259,6 @@
   </si>
   <si>
     <t>It's possible to use a bundle for other purposes (e.g. a document can be accepted as a transaction). This is primarily defined so that there can be specific rules for some of the bundle types.</t>
-  </si>
-  <si>
-    <t>transaction</t>
   </si>
   <si>
     <t>Indicates the purpose of a bundle - how it is intended to be used.</t>
@@ -1381,16 +1355,6 @@
     <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
   </si>
   <si>
-    <t>profile:resource}
-value:request.method}</t>
-  </si>
-  <si>
-    <t>Slicing based on the profile conformance of the entry</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
   </si>
@@ -1431,10 +1395,8 @@
     <t>Bundle.entry.resource</t>
   </si>
   <si>
-    <t>A resource in the bundle</t>
-  </si>
-  <si>
-    <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
+    <t xml:space="preserve">DocumentReference {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-documentreference}
+</t>
   </si>
   <si>
     <t>Bundle.entry.search</t>
@@ -1654,127 +1616,6 @@
   <si>
     <t>For a POST/PUT operation, this is the equivalent outcome that would be returned for prefer = operationoutcome - except that the resource is always returned whether or not the outcome is returned.
 This outcome is not used for error responses in batch/transaction, only for hints and warnings. In a batch operation, the error will be in Bundle.entry.response, and for transaction, there will be a single OperationOutcome instead of a bundle in the case of an error.</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents</t>
-  </si>
-  <si>
-    <t>Documents</t>
-  </si>
-  <si>
-    <t>the Documents</t>
-  </si>
-  <si>
-    <t>the Documents referenced by the DocumentReference resources</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.link</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.fullUrl</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binary {Binary}
-</t>
-  </si>
-  <si>
-    <t>Pure binary content defined by a format other than FHIR</t>
-  </si>
-  <si>
-    <t>A resource that represents the data of a single raw artifact as digital content accessible in its native format.  A Binary resource can contain any content, whether text, image, pdf, zip archive, etc.</t>
-  </si>
-  <si>
-    <t>Typically, Binary resources are used for handling content such as:  
-* CDA Documents (i.e. with XDS) 
-* PDF Documents 
-* Images (the Media resource is preferred for handling images, but not possible when the content is already binary - e.g. XDS).</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.search</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.search.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.search.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.search.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.search.mode</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.search.score</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.request</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.request.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.request.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.request.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.request.method</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.request.url</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.request.ifNoneMatch</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.request.ifModifiedSince</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.request.ifMatch</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.request.ifNoneExist</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.response</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.response.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.response.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.response.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.response.status</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.response.location</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.response.etag</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.response.lastModified</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Documents.response.outcome</t>
   </si>
   <si>
     <t>Bundle.signature</t>
@@ -2101,7 +1942,7 @@
         <v>2</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="23">
@@ -2109,7 +1950,7 @@
         <v>4</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="24">
@@ -2125,7 +1966,7 @@
         <v>8</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="26">
@@ -2133,7 +1974,7 @@
         <v>10</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="27">
@@ -2179,7 +2020,7 @@
         <v>21</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="33">
@@ -2215,7 +2056,7 @@
         <v>29</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="38">
@@ -2223,7 +2064,7 @@
         <v>31</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="39">
@@ -2249,13 +2090,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK151"/>
+  <dimension ref="A1:AK111"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="24.5078125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="50.828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="50.828125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="11.49609375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="39.9140625" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="2.2109375" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="2.2109375" customWidth="true" bestFit="true"/>
@@ -2269,7 +2109,7 @@
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="11.40234375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.73046875" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="35.69140625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
@@ -2278,12 +2118,13 @@
     <col min="26" max="26" width="168.19140625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="120.0625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="22.5078125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="50.03125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="10.26171875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="1.04296875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="6.9296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="5.62109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="44.0703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="2.2109375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" hidden="true" width="8.0" customWidth="false"/>
     <col min="18" max="18" width="20.703125" customWidth="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
   </cols>
@@ -8724,13 +8565,13 @@
         <v>37</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>189</v>
+        <v>360</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>192</v>
@@ -8803,10 +8644,10 @@
         <v>3</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -8829,16 +8670,16 @@
         <v>37</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" t="s" s="2">
@@ -8888,7 +8729,7 @@
         <v>37</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>38</v>
@@ -8905,13 +8746,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -8937,10 +8778,10 @@
         <v>40</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
@@ -8991,7 +8832,7 @@
         <v>37</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>38</v>
@@ -9003,18 +8844,18 @@
         <v>37</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9113,13 +8954,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -9216,13 +9057,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -9239,21 +9080,23 @@
         <v>37</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="P67" s="2"/>
       <c r="Q67" t="s" s="2">
         <v>37</v>
@@ -9302,7 +9145,7 @@
         <v>37</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>38</v>
@@ -9311,32 +9154,32 @@
         <v>46</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>37</v>
@@ -9348,16 +9191,16 @@
         <v>37</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="P68" s="2"/>
       <c r="Q68" t="s" s="2">
@@ -9383,54 +9226,54 @@
         <v>37</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="AA68" t="s" s="2">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="AB68" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="AD68" t="s" s="2">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="AE68" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -9453,16 +9296,16 @@
         <v>47</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>48</v>
+        <v>152</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>78</v>
+        <v>384</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>79</v>
+        <v>385</v>
       </c>
       <c r="P69" s="2"/>
       <c r="Q69" t="s" s="2">
@@ -9512,7 +9355,7 @@
         <v>37</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>80</v>
+        <v>382</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>38</v>
@@ -9529,13 +9372,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -9543,7 +9386,7 @@
       </c>
       <c r="F70" s="2"/>
       <c r="G70" t="s" s="2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>46</v>
@@ -9558,16 +9401,16 @@
         <v>47</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>83</v>
+        <v>387</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>84</v>
+        <v>388</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>85</v>
+        <v>389</v>
       </c>
       <c r="P70" s="2"/>
       <c r="Q70" t="s" s="2">
@@ -9593,13 +9436,13 @@
         <v>37</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>37</v>
+        <v>165</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>37</v>
+        <v>390</v>
       </c>
       <c r="AA70" t="s" s="2">
-        <v>37</v>
+        <v>391</v>
       </c>
       <c r="AB70" t="s" s="2">
         <v>37</v>
@@ -9617,10 +9460,10 @@
         <v>37</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>86</v>
+        <v>386</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>46</v>
@@ -9634,13 +9477,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -9663,16 +9506,16 @@
         <v>47</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>89</v>
+        <v>393</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>90</v>
+        <v>394</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>91</v>
+        <v>395</v>
       </c>
       <c r="P71" s="2"/>
       <c r="Q71" t="s" s="2">
@@ -9722,7 +9565,7 @@
         <v>37</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>92</v>
+        <v>392</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>38</v>
@@ -9739,13 +9582,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -9753,10 +9596,10 @@
       </c>
       <c r="F72" s="2"/>
       <c r="G72" t="s" s="2">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>37</v>
@@ -9768,16 +9611,16 @@
         <v>47</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>94</v>
+        <v>293</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>95</v>
+        <v>397</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>96</v>
+        <v>398</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>97</v>
+        <v>399</v>
       </c>
       <c r="P72" s="2"/>
       <c r="Q72" t="s" s="2">
@@ -9827,16 +9670,16 @@
         <v>37</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>98</v>
+        <v>396</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>58</v>
+        <v>400</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>59</v>
@@ -9844,13 +9687,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -9873,16 +9716,16 @@
         <v>47</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>100</v>
+        <v>215</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>101</v>
+        <v>402</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>102</v>
+        <v>403</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>103</v>
+        <v>404</v>
       </c>
       <c r="P73" s="2"/>
       <c r="Q73" t="s" s="2">
@@ -9908,13 +9751,13 @@
         <v>37</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="AA73" t="s" s="2">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="AB73" t="s" s="2">
         <v>37</v>
@@ -9932,7 +9775,7 @@
         <v>37</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>107</v>
+        <v>401</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>38</v>
@@ -9949,13 +9792,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -9966,7 +9809,7 @@
         <v>38</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>37</v>
@@ -9975,20 +9818,18 @@
         <v>37</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" s="2"/>
       <c r="Q74" t="s" s="2">
         <v>37</v>
@@ -10013,13 +9854,13 @@
         <v>37</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="AA74" t="s" s="2">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="AB74" t="s" s="2">
         <v>37</v>
@@ -10037,62 +9878,62 @@
         <v>37</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>59</v>
+        <v>37</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="P75" s="2"/>
       <c r="Q75" t="s" s="2">
@@ -10130,76 +9971,78 @@
         <v>37</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="AD75" t="s" s="2">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="AE75" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
-        <v>37</v>
+        <v>222</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>123</v>
+        <v>223</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="P76" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="Q76" t="s" s="2">
         <v>37</v>
       </c>
@@ -10223,13 +10066,13 @@
         <v>37</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>126</v>
+        <v>37</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>127</v>
+        <v>37</v>
       </c>
       <c r="AA76" t="s" s="2">
-        <v>128</v>
+        <v>37</v>
       </c>
       <c r="AB76" t="s" s="2">
         <v>37</v>
@@ -10247,30 +10090,30 @@
         <v>37</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>129</v>
+        <v>226</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -10278,7 +10121,7 @@
       </c>
       <c r="F77" s="2"/>
       <c r="G77" t="s" s="2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>46</v>
@@ -10293,16 +10136,16 @@
         <v>47</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>152</v>
+        <v>61</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>393</v>
+        <v>265</v>
       </c>
       <c r="P77" s="2"/>
       <c r="Q77" t="s" s="2">
@@ -10352,10 +10195,10 @@
         <v>37</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>46</v>
@@ -10369,13 +10212,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -10398,16 +10241,16 @@
         <v>47</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>396</v>
+        <v>413</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>397</v>
+        <v>414</v>
       </c>
       <c r="P78" s="2"/>
       <c r="Q78" t="s" s="2">
@@ -10418,7 +10261,7 @@
         <v>37</v>
       </c>
       <c r="T78" t="s" s="2">
-        <v>398</v>
+        <v>37</v>
       </c>
       <c r="U78" t="s" s="2">
         <v>37</v>
@@ -10433,13 +10276,13 @@
         <v>37</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>165</v>
+        <v>37</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>399</v>
+        <v>37</v>
       </c>
       <c r="AA78" t="s" s="2">
-        <v>400</v>
+        <v>37</v>
       </c>
       <c r="AB78" t="s" s="2">
         <v>37</v>
@@ -10457,7 +10300,7 @@
         <v>37</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>46</v>
@@ -10474,13 +10317,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -10488,10 +10331,10 @@
       </c>
       <c r="F79" s="2"/>
       <c r="G79" t="s" s="2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>37</v>
@@ -10503,17 +10346,15 @@
         <v>47</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" s="2"/>
       <c r="Q79" t="s" s="2">
         <v>37</v>
@@ -10562,30 +10403,30 @@
         <v>37</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>59</v>
+        <v>418</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -10605,20 +10446,18 @@
         <v>37</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>293</v>
+        <v>61</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>406</v>
+        <v>62</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" s="2"/>
       <c r="Q80" t="s" s="2">
         <v>37</v>
@@ -10667,7 +10506,7 @@
         <v>37</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>405</v>
+        <v>64</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>38</v>
@@ -10676,25 +10515,25 @@
         <v>46</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>409</v>
+        <v>37</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>59</v>
+        <v>37</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" t="s" s="2">
@@ -10710,19 +10549,19 @@
         <v>37</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>411</v>
+        <v>68</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>412</v>
+        <v>69</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>413</v>
+        <v>70</v>
       </c>
       <c r="P81" s="2"/>
       <c r="Q81" t="s" s="2">
@@ -10760,19 +10599,19 @@
         <v>37</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="AD81" t="s" s="2">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="AE81" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>410</v>
+        <v>74</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>38</v>
@@ -10784,50 +10623,54 @@
         <v>58</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
-        <v>37</v>
+        <v>222</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>62</v>
+        <v>223</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O82" s="2"/>
-      <c r="P82" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="Q82" t="s" s="2">
         <v>37</v>
       </c>
@@ -10875,34 +10718,34 @@
         <v>37</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>64</v>
+        <v>226</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>37</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" t="s" s="2">
@@ -10918,20 +10761,18 @@
         <v>37</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>68</v>
+        <v>423</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>70</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" s="2"/>
       <c r="Q83" t="s" s="2">
         <v>37</v>
@@ -10968,19 +10809,19 @@
         <v>37</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="AD83" t="s" s="2">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="AE83" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>74</v>
+        <v>422</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>38</v>
@@ -10989,57 +10830,55 @@
         <v>39</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>75</v>
+        <v>37</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
-        <v>222</v>
+        <v>37</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>47</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>223</v>
+        <v>426</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>224</v>
+        <v>427</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="P84" s="2"/>
       <c r="Q84" t="s" s="2">
         <v>37</v>
       </c>
@@ -11087,30 +10926,30 @@
         <v>37</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>226</v>
+        <v>425</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -11118,7 +10957,7 @@
       </c>
       <c r="F85" s="2"/>
       <c r="G85" t="s" s="2">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>46</v>
@@ -11130,19 +10969,19 @@
         <v>37</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>61</v>
+        <v>430</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>418</v>
+        <v>41</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>419</v>
+        <v>42</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>265</v>
+        <v>43</v>
       </c>
       <c r="P85" s="2"/>
       <c r="Q85" t="s" s="2">
@@ -11192,30 +11031,30 @@
         <v>37</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>46</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>59</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -11223,7 +11062,7 @@
       </c>
       <c r="F86" s="2"/>
       <c r="G86" t="s" s="2">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>46</v>
@@ -11238,17 +11077,15 @@
         <v>47</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>88</v>
+        <v>215</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" s="2"/>
       <c r="Q86" t="s" s="2">
         <v>37</v>
@@ -11297,16 +11134,16 @@
         <v>37</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>46</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>58</v>
+        <v>434</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>59</v>
@@ -11314,13 +11151,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -11331,25 +11168,25 @@
         <v>38</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J87" t="s" s="2">
         <v>37</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>215</v>
+        <v>61</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>425</v>
+        <v>62</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>426</v>
+        <v>63</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" s="2"/>
@@ -11388,53 +11225,53 @@
         <v>37</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>427</v>
+        <v>37</v>
       </c>
       <c r="AD87" t="s" s="2">
-        <v>428</v>
+        <v>37</v>
       </c>
       <c r="AE87" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>429</v>
+        <v>37</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>424</v>
+        <v>64</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>430</v>
+        <v>37</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>37</v>
@@ -11446,15 +11283,17 @@
         <v>37</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>70</v>
+      </c>
       <c r="P88" s="2"/>
       <c r="Q88" t="s" s="2">
         <v>37</v>
@@ -11491,46 +11330,46 @@
         <v>37</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="AD88" t="s" s="2">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="AE88" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>37</v>
+        <v>75</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
-        <v>66</v>
+        <v>222</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" t="s" s="2">
@@ -11543,24 +11382,26 @@
         <v>37</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>67</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>68</v>
+        <v>223</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>69</v>
+        <v>224</v>
       </c>
       <c r="O89" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="P89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="Q89" t="s" s="2">
         <v>37</v>
       </c>
@@ -11596,19 +11437,19 @@
         <v>37</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="AD89" t="s" s="2">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="AE89" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>74</v>
+        <v>226</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>38</v>
@@ -11625,49 +11466,47 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
-        <v>222</v>
+        <v>37</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="K90" t="s" s="2">
         <v>47</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>223</v>
+        <v>439</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>224</v>
+        <v>440</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="P90" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="P90" s="2"/>
       <c r="Q90" t="s" s="2">
         <v>37</v>
       </c>
@@ -11691,13 +11530,13 @@
         <v>37</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>37</v>
+        <v>165</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>37</v>
+        <v>442</v>
       </c>
       <c r="AA90" t="s" s="2">
-        <v>37</v>
+        <v>443</v>
       </c>
       <c r="AB90" t="s" s="2">
         <v>37</v>
@@ -11715,30 +11554,30 @@
         <v>37</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>226</v>
+        <v>438</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -11749,7 +11588,7 @@
         <v>38</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>37</v>
@@ -11761,15 +11600,17 @@
         <v>47</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>37</v>
+        <v>445</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="P91" s="2"/>
       <c r="Q91" t="s" s="2">
         <v>37</v>
@@ -11818,30 +11659,30 @@
         <v>37</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -11864,17 +11705,15 @@
         <v>47</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>88</v>
+        <v>215</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="O92" s="2"/>
       <c r="P92" s="2"/>
       <c r="Q92" t="s" s="2">
         <v>37</v>
@@ -11923,7 +11762,7 @@
         <v>37</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>38</v>
@@ -11932,7 +11771,7 @@
         <v>46</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>58</v>
+        <v>452</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>59</v>
@@ -11940,13 +11779,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -11960,22 +11799,22 @@
         <v>46</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J93" t="s" s="2">
         <v>37</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>442</v>
+        <v>62</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>443</v>
+        <v>63</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" s="2"/>
@@ -12026,7 +11865,7 @@
         <v>37</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>441</v>
+        <v>64</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>38</v>
@@ -12043,24 +11882,24 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>37</v>
@@ -12069,18 +11908,20 @@
         <v>37</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>445</v>
+        <v>68</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O94" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>70</v>
+      </c>
       <c r="P94" s="2"/>
       <c r="Q94" t="s" s="2">
         <v>37</v>
@@ -12117,74 +11958,78 @@
         <v>37</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="AD94" t="s" s="2">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="AE94" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>444</v>
+        <v>74</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>447</v>
+        <v>58</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
-        <v>37</v>
+        <v>222</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>62</v>
+        <v>223</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O95" s="2"/>
-      <c r="P95" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="Q95" t="s" s="2">
         <v>37</v>
       </c>
@@ -12232,41 +12077,41 @@
         <v>37</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>64</v>
+        <v>226</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>37</v>
+        <v>75</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" t="s" s="2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>37</v>
@@ -12275,19 +12120,19 @@
         <v>37</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>68</v>
+        <v>457</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>69</v>
+        <v>458</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>70</v>
+        <v>265</v>
       </c>
       <c r="P96" s="2"/>
       <c r="Q96" t="s" s="2">
@@ -12313,90 +12158,88 @@
         <v>37</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>37</v>
+        <v>165</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>37</v>
+        <v>459</v>
       </c>
       <c r="AA96" t="s" s="2">
-        <v>37</v>
+        <v>460</v>
       </c>
       <c r="AB96" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="AD96" t="s" s="2">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="AE96" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>74</v>
+        <v>456</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
-        <v>222</v>
+        <v>37</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" t="s" s="2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="K97" t="s" s="2">
         <v>47</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>223</v>
+        <v>462</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>224</v>
+        <v>463</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="P97" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="P97" s="2"/>
       <c r="Q97" t="s" s="2">
         <v>37</v>
       </c>
@@ -12444,30 +12287,30 @@
         <v>37</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>226</v>
+        <v>461</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -12490,16 +12333,16 @@
         <v>47</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>454</v>
+        <v>265</v>
       </c>
       <c r="P98" s="2"/>
       <c r="Q98" t="s" s="2">
@@ -12525,13 +12368,13 @@
         <v>37</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>165</v>
+        <v>37</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>455</v>
+        <v>37</v>
       </c>
       <c r="AA98" t="s" s="2">
-        <v>456</v>
+        <v>37</v>
       </c>
       <c r="AB98" t="s" s="2">
         <v>37</v>
@@ -12549,7 +12392,7 @@
         <v>37</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>38</v>
@@ -12566,13 +12409,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -12595,16 +12438,16 @@
         <v>47</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="P99" s="2"/>
       <c r="Q99" t="s" s="2">
@@ -12654,7 +12497,7 @@
         <v>37</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>38</v>
@@ -12671,13 +12514,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -12700,15 +12543,17 @@
         <v>47</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>215</v>
+        <v>61</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="O100" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P100" s="2"/>
       <c r="Q100" t="s" s="2">
         <v>37</v>
@@ -12757,7 +12602,7 @@
         <v>37</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>38</v>
@@ -12766,7 +12611,7 @@
         <v>46</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>465</v>
+        <v>58</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>59</v>
@@ -12774,13 +12619,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -12800,18 +12645,20 @@
         <v>37</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L101" t="s" s="2">
         <v>61</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>62</v>
+        <v>475</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O101" s="2"/>
+        <v>476</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P101" s="2"/>
       <c r="Q101" t="s" s="2">
         <v>37</v>
@@ -12860,7 +12707,7 @@
         <v>37</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>64</v>
+        <v>474</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>38</v>
@@ -12869,32 +12716,32 @@
         <v>46</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>37</v>
@@ -12903,20 +12750,18 @@
         <v>37</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>67</v>
+        <v>215</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>68</v>
+        <v>478</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>70</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="O102" s="2"/>
       <c r="P102" s="2"/>
       <c r="Q102" t="s" s="2">
         <v>37</v>
@@ -12953,78 +12798,74 @@
         <v>37</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="AD102" t="s" s="2">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="AE102" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>74</v>
+        <v>477</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>58</v>
+        <v>480</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
-        <v>222</v>
+        <v>37</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>223</v>
+        <v>62</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="P103" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="O103" s="2"/>
+      <c r="P103" s="2"/>
       <c r="Q103" t="s" s="2">
         <v>37</v>
       </c>
@@ -13072,41 +12913,41 @@
         <v>37</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>226</v>
+        <v>64</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>75</v>
+        <v>37</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" t="s" s="2">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>37</v>
@@ -13115,19 +12956,19 @@
         <v>37</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>470</v>
+        <v>68</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>471</v>
+        <v>69</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>265</v>
+        <v>70</v>
       </c>
       <c r="P104" s="2"/>
       <c r="Q104" t="s" s="2">
@@ -13153,88 +12994,90 @@
         <v>37</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>165</v>
+        <v>37</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>472</v>
+        <v>37</v>
       </c>
       <c r="AA104" t="s" s="2">
-        <v>473</v>
+        <v>37</v>
       </c>
       <c r="AB104" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="AD104" t="s" s="2">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="AE104" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>469</v>
+        <v>74</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
-        <v>37</v>
+        <v>222</v>
       </c>
       <c r="F105" s="2"/>
       <c r="G105" t="s" s="2">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="K105" t="s" s="2">
         <v>47</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>475</v>
+        <v>223</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>476</v>
+        <v>224</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="P105" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="P105" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="Q105" t="s" s="2">
         <v>37</v>
       </c>
@@ -13282,30 +13125,30 @@
         <v>37</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>474</v>
+        <v>226</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -13313,7 +13156,7 @@
       </c>
       <c r="F106" s="2"/>
       <c r="G106" t="s" s="2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>46</v>
@@ -13331,10 +13174,10 @@
         <v>61</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="O106" t="s" s="2">
         <v>265</v>
@@ -13387,10 +13230,10 @@
         <v>37</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>46</v>
@@ -13404,13 +13247,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -13433,16 +13276,16 @@
         <v>47</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>483</v>
+        <v>414</v>
       </c>
       <c r="P107" s="2"/>
       <c r="Q107" t="s" s="2">
@@ -13492,7 +13335,7 @@
         <v>37</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>38</v>
@@ -13509,13 +13352,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -13541,13 +13384,13 @@
         <v>61</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>265</v>
+        <v>493</v>
       </c>
       <c r="P108" s="2"/>
       <c r="Q108" t="s" s="2">
@@ -13597,7 +13440,7 @@
         <v>37</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>38</v>
@@ -13614,13 +13457,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -13643,16 +13486,16 @@
         <v>47</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>265</v>
+        <v>497</v>
       </c>
       <c r="P109" s="2"/>
       <c r="Q109" t="s" s="2">
@@ -13702,7 +13545,7 @@
         <v>37</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>38</v>
@@ -13719,13 +13562,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -13748,15 +13591,17 @@
         <v>47</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>215</v>
+        <v>139</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O110" s="2"/>
+        <v>500</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>501</v>
+      </c>
       <c r="P110" s="2"/>
       <c r="Q110" t="s" s="2">
         <v>37</v>
@@ -13805,7 +13650,7 @@
         <v>37</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>38</v>
@@ -13814,21 +13659,21 @@
         <v>46</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>493</v>
+        <v>37</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>59</v>
+        <v>37</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -13848,19 +13693,23 @@
         <v>37</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>61</v>
+        <v>503</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>62</v>
+        <v>504</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O111" s="2"/>
-      <c r="P111" s="2"/>
+        <v>505</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>507</v>
+      </c>
       <c r="Q111" t="s" s="2">
         <v>37</v>
       </c>
@@ -13908,7 +13757,7 @@
         <v>37</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>64</v>
+        <v>502</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>38</v>
@@ -13917,4205 +13766,9 @@
         <v>46</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="D112" s="2"/>
-      <c r="E112" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="F112" s="2"/>
-      <c r="G112" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="P112" s="2"/>
-      <c r="Q112" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R112" s="2"/>
-      <c r="S112" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="C113" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="D113" s="2"/>
-      <c r="E113" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="F113" s="2"/>
-      <c r="G113" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="P113" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Q113" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R113" s="2"/>
-      <c r="S113" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="C114" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="D114" s="2"/>
-      <c r="E114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F114" s="2"/>
-      <c r="G114" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="P114" s="2"/>
-      <c r="Q114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R114" s="2"/>
-      <c r="S114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="C115" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="D115" s="2"/>
-      <c r="E115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F115" s="2"/>
-      <c r="G115" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="P115" s="2"/>
-      <c r="Q115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R115" s="2"/>
-      <c r="S115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="D116" s="2"/>
-      <c r="E116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F116" s="2"/>
-      <c r="G116" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="P116" s="2"/>
-      <c r="Q116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R116" s="2"/>
-      <c r="S116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="D117" s="2"/>
-      <c r="E117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F117" s="2"/>
-      <c r="G117" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="P117" s="2"/>
-      <c r="Q117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R117" s="2"/>
-      <c r="S117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="D118" s="2"/>
-      <c r="E118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F118" s="2"/>
-      <c r="G118" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="P118" s="2"/>
-      <c r="Q118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R118" s="2"/>
-      <c r="S118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="D119" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="E119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F119" s="2"/>
-      <c r="G119" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="O119" s="2"/>
-      <c r="P119" s="2"/>
-      <c r="Q119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R119" s="2"/>
-      <c r="S119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="C120" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="D120" s="2"/>
-      <c r="E120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F120" s="2"/>
-      <c r="G120" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O120" s="2"/>
-      <c r="P120" s="2"/>
-      <c r="Q120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R120" s="2"/>
-      <c r="S120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C121" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="D121" s="2"/>
-      <c r="E121" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="F121" s="2"/>
-      <c r="G121" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="P121" s="2"/>
-      <c r="Q121" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R121" s="2"/>
-      <c r="S121" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C122" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="D122" s="2"/>
-      <c r="E122" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="F122" s="2"/>
-      <c r="G122" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="P122" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Q122" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R122" s="2"/>
-      <c r="S122" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="C123" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="D123" s="2"/>
-      <c r="E123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F123" s="2"/>
-      <c r="G123" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O123" s="2"/>
-      <c r="P123" s="2"/>
-      <c r="Q123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R123" s="2"/>
-      <c r="S123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="C124" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="D124" s="2"/>
-      <c r="E124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F124" s="2"/>
-      <c r="G124" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="P124" s="2"/>
-      <c r="Q124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R124" s="2"/>
-      <c r="S124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="C125" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="D125" s="2"/>
-      <c r="E125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F125" s="2"/>
-      <c r="G125" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="P125" s="2"/>
-      <c r="Q125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R125" s="2"/>
-      <c r="S125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="C126" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="D126" s="2"/>
-      <c r="E126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F126" s="2"/>
-      <c r="G126" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O126" s="2"/>
-      <c r="P126" s="2"/>
-      <c r="Q126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R126" s="2"/>
-      <c r="S126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C127" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="D127" s="2"/>
-      <c r="E127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F127" s="2"/>
-      <c r="G127" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O127" s="2"/>
-      <c r="P127" s="2"/>
-      <c r="Q127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R127" s="2"/>
-      <c r="S127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="C128" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="D128" s="2"/>
-      <c r="E128" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="F128" s="2"/>
-      <c r="G128" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="P128" s="2"/>
-      <c r="Q128" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R128" s="2"/>
-      <c r="S128" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="C129" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="D129" s="2"/>
-      <c r="E129" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="F129" s="2"/>
-      <c r="G129" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L129" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="P129" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Q129" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R129" s="2"/>
-      <c r="S129" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="AJ129" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK129" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="C130" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="D130" s="2"/>
-      <c r="E130" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F130" s="2"/>
-      <c r="G130" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H130" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I130" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J130" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K130" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L130" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="P130" s="2"/>
-      <c r="Q130" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R130" s="2"/>
-      <c r="S130" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T130" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U130" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V130" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W130" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X130" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG130" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AH130" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI130" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ130" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK130" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="C131" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="D131" s="2"/>
-      <c r="E131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F131" s="2"/>
-      <c r="G131" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H131" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K131" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L131" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="P131" s="2"/>
-      <c r="Q131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R131" s="2"/>
-      <c r="S131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ131" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK131" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C132" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="D132" s="2"/>
-      <c r="E132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F132" s="2"/>
-      <c r="G132" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K132" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L132" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="O132" s="2"/>
-      <c r="P132" s="2"/>
-      <c r="Q132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R132" s="2"/>
-      <c r="S132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AK132" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C133" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="D133" s="2"/>
-      <c r="E133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F133" s="2"/>
-      <c r="G133" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H133" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="L133" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O133" s="2"/>
-      <c r="P133" s="2"/>
-      <c r="Q133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R133" s="2"/>
-      <c r="S133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ133" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK133" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="C134" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="D134" s="2"/>
-      <c r="E134" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="F134" s="2"/>
-      <c r="G134" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="P134" s="2"/>
-      <c r="Q134" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R134" s="2"/>
-      <c r="S134" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK134" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C135" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="D135" s="2"/>
-      <c r="E135" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="F135" s="2"/>
-      <c r="G135" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="P135" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Q135" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R135" s="2"/>
-      <c r="S135" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK135" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="C136" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="D136" s="2"/>
-      <c r="E136" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F136" s="2"/>
-      <c r="G136" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="H136" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J136" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K136" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="P136" s="2"/>
-      <c r="Q136" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R136" s="2"/>
-      <c r="S136" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T136" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U136" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V136" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W136" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X136" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="Z136" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG136" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="AH136" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AI136" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ136" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C137" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="D137" s="2"/>
-      <c r="E137" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F137" s="2"/>
-      <c r="G137" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="H137" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I137" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J137" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K137" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L137" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="P137" s="2"/>
-      <c r="Q137" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R137" s="2"/>
-      <c r="S137" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T137" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U137" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V137" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W137" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X137" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z137" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA137" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF137" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="C138" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="D138" s="2"/>
-      <c r="E138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F138" s="2"/>
-      <c r="G138" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H138" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K138" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L138" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="P138" s="2"/>
-      <c r="Q138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R138" s="2"/>
-      <c r="S138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG138" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AH138" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI138" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ138" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK138" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="C139" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="D139" s="2"/>
-      <c r="E139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F139" s="2"/>
-      <c r="G139" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H139" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K139" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="P139" s="2"/>
-      <c r="Q139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R139" s="2"/>
-      <c r="S139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG139" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AH139" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI139" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ139" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK139" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C140" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="D140" s="2"/>
-      <c r="E140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F140" s="2"/>
-      <c r="G140" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H140" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K140" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L140" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="P140" s="2"/>
-      <c r="Q140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R140" s="2"/>
-      <c r="S140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG140" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AH140" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI140" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ140" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK140" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="C141" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="D141" s="2"/>
-      <c r="E141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F141" s="2"/>
-      <c r="G141" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H141" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K141" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L141" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="P141" s="2"/>
-      <c r="Q141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R141" s="2"/>
-      <c r="S141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG141" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AH141" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI141" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ141" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK141" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="C142" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="D142" s="2"/>
-      <c r="E142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F142" s="2"/>
-      <c r="G142" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H142" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K142" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L142" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O142" s="2"/>
-      <c r="P142" s="2"/>
-      <c r="Q142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R142" s="2"/>
-      <c r="S142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG142" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AH142" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI142" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ142" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AK142" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C143" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="D143" s="2"/>
-      <c r="E143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F143" s="2"/>
-      <c r="G143" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H143" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="L143" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O143" s="2"/>
-      <c r="P143" s="2"/>
-      <c r="Q143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R143" s="2"/>
-      <c r="S143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG143" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="AH143" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI143" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ143" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK143" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="C144" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="D144" s="2"/>
-      <c r="E144" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="F144" s="2"/>
-      <c r="G144" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H144" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="I144" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J144" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K144" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="L144" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="P144" s="2"/>
-      <c r="Q144" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R144" s="2"/>
-      <c r="S144" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T144" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U144" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V144" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W144" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X144" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y144" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z144" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA144" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB144" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD144" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE144" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF144" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG144" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH144" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI144" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="AJ144" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK144" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B145" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="C145" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="D145" s="2"/>
-      <c r="E145" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="F145" s="2"/>
-      <c r="G145" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H145" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="I145" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J145" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="K145" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L145" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="P145" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Q145" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R145" s="2"/>
-      <c r="S145" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T145" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U145" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V145" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W145" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X145" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y145" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z145" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA145" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB145" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC145" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD145" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE145" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF145" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG145" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AH145" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI145" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="AJ145" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK145" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="C146" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="D146" s="2"/>
-      <c r="E146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F146" s="2"/>
-      <c r="G146" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="H146" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K146" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L146" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="P146" s="2"/>
-      <c r="Q146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R146" s="2"/>
-      <c r="S146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG146" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AH146" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AI146" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ146" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK146" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B147" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C147" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="D147" s="2"/>
-      <c r="E147" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F147" s="2"/>
-      <c r="G147" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H147" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I147" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J147" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K147" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L147" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="P147" s="2"/>
-      <c r="Q147" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R147" s="2"/>
-      <c r="S147" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T147" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U147" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V147" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W147" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X147" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y147" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z147" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA147" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB147" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC147" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD147" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE147" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF147" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG147" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AH147" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI147" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ147" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK147" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B148" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="C148" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="D148" s="2"/>
-      <c r="E148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F148" s="2"/>
-      <c r="G148" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H148" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K148" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L148" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="P148" s="2"/>
-      <c r="Q148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R148" s="2"/>
-      <c r="S148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG148" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AH148" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI148" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ148" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK148" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B149" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C149" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="D149" s="2"/>
-      <c r="E149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F149" s="2"/>
-      <c r="G149" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H149" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K149" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="P149" s="2"/>
-      <c r="Q149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R149" s="2"/>
-      <c r="S149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG149" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AH149" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI149" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ149" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK149" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B150" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C150" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="D150" s="2"/>
-      <c r="E150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F150" s="2"/>
-      <c r="G150" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H150" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K150" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L150" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="P150" s="2"/>
-      <c r="Q150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R150" s="2"/>
-      <c r="S150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG150" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AH150" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI150" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK150" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B151" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="C151" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="D151" s="2"/>
-      <c r="E151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F151" s="2"/>
-      <c r="G151" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H151" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="I151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K151" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L151" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="P151" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="Q151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="R151" s="2"/>
-      <c r="S151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="T151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="U151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="V151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="W151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="X151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AG151" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AH151" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AI151" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AJ151" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK151" t="s" s="2">
         <v>59</v>
       </c>
     </row>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-21T14:50:45+00:00</t>
+    <t>2023-09-22T07:44:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-22T07:44:14+00:00</t>
+    <t>2023-09-22T09:20:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-22T09:20:33+00:00</t>
+    <t>2023-09-22T09:23:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3731" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3731" uniqueCount="510">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-22T09:23:37+00:00</t>
+    <t>2023-09-22T12:19:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1261,6 +1261,9 @@
     <t>It's possible to use a bundle for other purposes (e.g. a document can be accepted as a transaction). This is primarily defined so that there can be specific rules for some of the bundle types.</t>
   </si>
   <si>
+    <t>transaction</t>
+  </si>
+  <si>
     <t>Indicates the purpose of a bundle - how it is intended to be used.</t>
   </si>
   <si>
@@ -1485,6 +1488,9 @@
   </si>
   <si>
     <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
+  </si>
+  <si>
+    <t>POST</t>
   </si>
   <si>
     <t>HTTP verbs (in the HTTP command line). See [HTTP rfc](https://tools.ietf.org/html/rfc7231) for details.</t>
@@ -2109,7 +2115,7 @@
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.73046875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="11.40234375" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="35.69140625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
@@ -9421,7 +9427,7 @@
         <v>37</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>37</v>
+        <v>390</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>37</v>
@@ -9439,10 +9445,10 @@
         <v>165</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA70" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AB70" t="s" s="2">
         <v>37</v>
@@ -9480,10 +9486,10 @@
         <v>368</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -9509,13 +9515,13 @@
         <v>82</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P71" s="2"/>
       <c r="Q71" t="s" s="2">
@@ -9565,7 +9571,7 @@
         <v>37</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>38</v>
@@ -9585,10 +9591,10 @@
         <v>368</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -9614,13 +9620,13 @@
         <v>293</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P72" s="2"/>
       <c r="Q72" t="s" s="2">
@@ -9670,7 +9676,7 @@
         <v>37</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>38</v>
@@ -9679,7 +9685,7 @@
         <v>46</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>59</v>
@@ -9690,10 +9696,10 @@
         <v>368</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -9719,13 +9725,13 @@
         <v>215</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P73" s="2"/>
       <c r="Q73" t="s" s="2">
@@ -9775,7 +9781,7 @@
         <v>37</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>38</v>
@@ -9795,10 +9801,10 @@
         <v>368</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -9898,10 +9904,10 @@
         <v>368</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10003,10 +10009,10 @@
         <v>368</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10110,10 +10116,10 @@
         <v>368</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -10139,10 +10145,10 @@
         <v>61</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O77" t="s" s="2">
         <v>265</v>
@@ -10195,7 +10201,7 @@
         <v>37</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>46</v>
@@ -10215,10 +10221,10 @@
         <v>368</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -10244,13 +10250,13 @@
         <v>88</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P78" s="2"/>
       <c r="Q78" t="s" s="2">
@@ -10300,7 +10306,7 @@
         <v>37</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>46</v>
@@ -10320,10 +10326,10 @@
         <v>368</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -10349,10 +10355,10 @@
         <v>215</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
@@ -10403,7 +10409,7 @@
         <v>37</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>38</v>
@@ -10415,7 +10421,7 @@
         <v>58</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="80">
@@ -10423,10 +10429,10 @@
         <v>368</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -10526,10 +10532,10 @@
         <v>368</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -10631,10 +10637,10 @@
         <v>368</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -10738,10 +10744,10 @@
         <v>368</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -10767,10 +10773,10 @@
         <v>40</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" s="2"/>
@@ -10821,7 +10827,7 @@
         <v>37</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>38</v>
@@ -10841,10 +10847,10 @@
         <v>368</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -10870,13 +10876,13 @@
         <v>88</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P84" s="2"/>
       <c r="Q84" t="s" s="2">
@@ -10926,7 +10932,7 @@
         <v>37</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>38</v>
@@ -10946,10 +10952,10 @@
         <v>368</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -10957,7 +10963,7 @@
       </c>
       <c r="F85" s="2"/>
       <c r="G85" t="s" s="2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>46</v>
@@ -10972,7 +10978,7 @@
         <v>37</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M85" t="s" s="2">
         <v>41</v>
@@ -11031,7 +11037,7 @@
         <v>37</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>38</v>
@@ -11051,10 +11057,10 @@
         <v>368</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -11080,10 +11086,10 @@
         <v>215</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" s="2"/>
@@ -11134,7 +11140,7 @@
         <v>37</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>38</v>
@@ -11143,7 +11149,7 @@
         <v>46</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>59</v>
@@ -11154,10 +11160,10 @@
         <v>368</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -11257,10 +11263,10 @@
         <v>368</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -11362,10 +11368,10 @@
         <v>368</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -11469,10 +11475,10 @@
         <v>368</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -11498,13 +11504,13 @@
         <v>122</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P90" s="2"/>
       <c r="Q90" t="s" s="2">
@@ -11533,10 +11539,10 @@
         <v>165</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA90" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AB90" t="s" s="2">
         <v>37</v>
@@ -11554,7 +11560,7 @@
         <v>37</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>38</v>
@@ -11574,10 +11580,10 @@
         <v>368</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -11600,16 +11606,16 @@
         <v>47</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P91" s="2"/>
       <c r="Q91" t="s" s="2">
@@ -11659,7 +11665,7 @@
         <v>37</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>38</v>
@@ -11679,10 +11685,10 @@
         <v>368</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -11708,10 +11714,10 @@
         <v>215</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
@@ -11762,7 +11768,7 @@
         <v>37</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>38</v>
@@ -11771,7 +11777,7 @@
         <v>46</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>59</v>
@@ -11782,10 +11788,10 @@
         <v>368</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -11885,10 +11891,10 @@
         <v>368</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -11990,10 +11996,10 @@
         <v>368</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -12097,10 +12103,10 @@
         <v>368</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -12126,10 +12132,10 @@
         <v>122</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O96" t="s" s="2">
         <v>265</v>
@@ -12143,7 +12149,7 @@
         <v>37</v>
       </c>
       <c r="T96" t="s" s="2">
-        <v>37</v>
+        <v>460</v>
       </c>
       <c r="U96" t="s" s="2">
         <v>37</v>
@@ -12161,10 +12167,10 @@
         <v>165</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AA96" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AB96" t="s" s="2">
         <v>37</v>
@@ -12182,7 +12188,7 @@
         <v>37</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>46</v>
@@ -12202,10 +12208,10 @@
         <v>368</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -12231,13 +12237,13 @@
         <v>88</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="P97" s="2"/>
       <c r="Q97" t="s" s="2">
@@ -12287,7 +12293,7 @@
         <v>37</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>46</v>
@@ -12307,10 +12313,10 @@
         <v>368</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -12336,10 +12342,10 @@
         <v>61</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="O98" t="s" s="2">
         <v>265</v>
@@ -12392,7 +12398,7 @@
         <v>37</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>38</v>
@@ -12412,10 +12418,10 @@
         <v>368</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -12441,13 +12447,13 @@
         <v>82</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="P99" s="2"/>
       <c r="Q99" t="s" s="2">
@@ -12497,7 +12503,7 @@
         <v>37</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>38</v>
@@ -12517,10 +12523,10 @@
         <v>368</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -12546,10 +12552,10 @@
         <v>61</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="O100" t="s" s="2">
         <v>265</v>
@@ -12602,7 +12608,7 @@
         <v>37</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>38</v>
@@ -12622,10 +12628,10 @@
         <v>368</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -12651,10 +12657,10 @@
         <v>61</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O101" t="s" s="2">
         <v>265</v>
@@ -12707,7 +12713,7 @@
         <v>37</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>38</v>
@@ -12727,10 +12733,10 @@
         <v>368</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -12756,10 +12762,10 @@
         <v>215</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" s="2"/>
@@ -12810,7 +12816,7 @@
         <v>37</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>38</v>
@@ -12819,7 +12825,7 @@
         <v>46</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>59</v>
@@ -12830,10 +12836,10 @@
         <v>368</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -12933,10 +12939,10 @@
         <v>368</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -13038,10 +13044,10 @@
         <v>368</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -13145,10 +13151,10 @@
         <v>368</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -13174,10 +13180,10 @@
         <v>61</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O106" t="s" s="2">
         <v>265</v>
@@ -13230,7 +13236,7 @@
         <v>37</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>46</v>
@@ -13250,10 +13256,10 @@
         <v>368</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -13279,13 +13285,13 @@
         <v>88</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P107" s="2"/>
       <c r="Q107" t="s" s="2">
@@ -13335,7 +13341,7 @@
         <v>37</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>38</v>
@@ -13355,10 +13361,10 @@
         <v>368</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -13384,13 +13390,13 @@
         <v>61</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="P108" s="2"/>
       <c r="Q108" t="s" s="2">
@@ -13440,7 +13446,7 @@
         <v>37</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>38</v>
@@ -13460,10 +13466,10 @@
         <v>368</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -13489,13 +13495,13 @@
         <v>82</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="P109" s="2"/>
       <c r="Q109" t="s" s="2">
@@ -13545,7 +13551,7 @@
         <v>37</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>38</v>
@@ -13565,10 +13571,10 @@
         <v>368</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -13594,13 +13600,13 @@
         <v>139</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="P110" s="2"/>
       <c r="Q110" t="s" s="2">
@@ -13650,7 +13656,7 @@
         <v>37</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>38</v>
@@ -13670,10 +13676,10 @@
         <v>368</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -13696,19 +13702,19 @@
         <v>47</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="P111" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="Q111" t="s" s="2">
         <v>37</v>
@@ -13757,7 +13763,7 @@
         <v>37</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>38</v>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-22T12:19:21+00:00</t>
+    <t>2023-09-25T11:57:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-02T07:48:38+00:00</t>
+    <t>2023-10-02T08:19:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3731" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4782" uniqueCount="548">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-02T08:19:52+00:00</t>
+    <t>2023-10-02T10:10:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -452,6 +452,13 @@
     <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
   </si>
   <si>
+    <t xml:space="preserve">profile:resource}
+</t>
+  </si>
+  <si>
+    <t>Slicing based on the profile conformance of the entry</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
   </si>
@@ -492,6 +499,262 @@
     <t>Bundle.entry.resource</t>
   </si>
   <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>A resource in the bundle</t>
+  </si>
+  <si>
+    <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search</t>
+  </si>
+  <si>
+    <t>Search related information</t>
+  </si>
+  <si>
+    <t>Information about the search process that lead to the creation of this entry.</t>
+  </si>
+  <si>
+    <t>ele-1
+bdl-2</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.mode</t>
+  </si>
+  <si>
+    <t>match | include | outcome - why this is in the result set</t>
+  </si>
+  <si>
+    <t>Why this entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
+  </si>
+  <si>
+    <t>There is only one mode. In some corner cases, a resource may be included because it is both a match and an include. In these circumstances, 'match' takes precedence.</t>
+  </si>
+  <si>
+    <t>Why an entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/search-entry-mode|4.0.1</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Search ranking (between 0 and 1)</t>
+  </si>
+  <si>
+    <t>When searching, the server's search ranking score for the entry.</t>
+  </si>
+  <si>
+    <t>Servers are not required to return a ranking score. 1 is most relevant, and 0 is least relevant. Often, search results are sorted by score, but the client may specify a different sort order.
+See [Patient Match](http://hl7.org/fhir/R4/patient-operation-match.html) for the EMPI search which relates to this element.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request</t>
+  </si>
+  <si>
+    <t>Additional execution information (transaction/batch/history)</t>
+  </si>
+  <si>
+    <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
+  </si>
+  <si>
+    <t>ele-1
+bdl-3</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.method</t>
+  </si>
+  <si>
+    <t>GET | HEAD | POST | PUT | DELETE | PATCH</t>
+  </si>
+  <si>
+    <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
+  </si>
+  <si>
+    <t>HTTP verbs (in the HTTP command line). See [HTTP rfc](https://tools.ietf.org/html/rfc7231) for details.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/http-verb|4.0.1</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.url</t>
+  </si>
+  <si>
+    <t>URL for HTTP equivalent of this entry</t>
+  </si>
+  <si>
+    <t>The URL for this entry, relative to the root (the address to which the request is posted).</t>
+  </si>
+  <si>
+    <t>E.g. for a Patient Create, the method would be "POST" and the URL would be "Patient". For a Patient Update, the method would be PUT and the URL would be "Patient/[id]".</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifNoneMatch</t>
+  </si>
+  <si>
+    <t>For managing cache currency</t>
+  </si>
+  <si>
+    <t>If the ETag values match, return a 304 Not Modified status. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifModifiedSince</t>
+  </si>
+  <si>
+    <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
+  </si>
+  <si>
+    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifMatch</t>
+  </si>
+  <si>
+    <t>For managing update contention</t>
+  </si>
+  <si>
+    <t>Only perform the operation if the Etag value matches. For more information, see the API section ["Managing Resource Contention"](http://hl7.org/fhir/R4/http.html#concurrency).</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifNoneExist</t>
+  </si>
+  <si>
+    <t>For conditional creates</t>
+  </si>
+  <si>
+    <t>Instruct the server not to perform the create if a specified resource already exists. For further information, see the API documentation for ["Conditional Create"](http://hl7.org/fhir/R4/http.html#ccreate). This is just the query portion of the URL - what follows the "?" (not including the "?").</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response</t>
+  </si>
+  <si>
+    <t>Results of execution (transaction/batch/history)</t>
+  </si>
+  <si>
+    <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
+  </si>
+  <si>
+    <t>ele-1
+bdl-4</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.status</t>
+  </si>
+  <si>
+    <t>Status response code (text optional)</t>
+  </si>
+  <si>
+    <t>The status code returned by processing this entry. The status SHALL start with a 3 digit HTTP code (e.g. 404) and may contain the standard HTTP description associated with the status code.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.location</t>
+  </si>
+  <si>
+    <t>The location (if the operation returns a location)</t>
+  </si>
+  <si>
+    <t>The location header created by processing this operation, populated if the operation returns a location.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.etag</t>
+  </si>
+  <si>
+    <t>The Etag for the resource (if relevant)</t>
+  </si>
+  <si>
+    <t>The Etag for the resource, if the operation for the entry produced a versioned resource (see [Resource Metadata and Versioning](http://hl7.org/fhir/R4/http.html#versioning) and [Managing Resource Contention](http://hl7.org/fhir/R4/http.html#concurrency)).</t>
+  </si>
+  <si>
+    <t>Etags match the Resource.meta.versionId. The ETag has to match the version id in the header if a resource is included.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.lastModified</t>
+  </si>
+  <si>
+    <t>Server's date time modified</t>
+  </si>
+  <si>
+    <t>The date/time that the resource was modified on the server.</t>
+  </si>
+  <si>
+    <t>This has to match the same time in the meta header (meta.lastUpdated) if a resource is included.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.outcome</t>
+  </si>
+  <si>
+    <t>OperationOutcome with hints and warnings (for batch/transaction)</t>
+  </si>
+  <si>
+    <t>An OperationOutcome containing hints and warnings produced as part of processing this entry in a batch or transaction.</t>
+  </si>
+  <si>
+    <t>For a POST/PUT operation, this is the equivalent outcome that would be returned for prefer = operationoutcome - except that the resource is always returned whether or not the outcome is returned.
+This outcome is not used for error responses in batch/transaction, only for hints and warnings. In a batch operation, the error will be in Bundle.entry.response, and for transaction, there will be a single OperationOutcome instead of a bundle in the case of an error.</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference</t>
+  </si>
+  <si>
+    <t>DUIDocumentReference</t>
+  </si>
+  <si>
+    <t>DocumentReference conforming to the TDDUIDocumentReference profile, used to convey a document in CDA format.</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.link</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.fullUrl</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.resource</t>
+  </si>
+  <si>
     <t xml:space="preserve">DocumentReference {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-documentreference}
 </t>
   </si>
@@ -509,230 +772,82 @@
 dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
-    <t>Bundle.entry.search</t>
-  </si>
-  <si>
-    <t>Search related information</t>
-  </si>
-  <si>
-    <t>Information about the search process that lead to the creation of this entry.</t>
-  </si>
-  <si>
-    <t>ele-1
-bdl-2</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.mode</t>
-  </si>
-  <si>
-    <t>match | include | outcome - why this is in the result set</t>
-  </si>
-  <si>
-    <t>Why this entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
-  </si>
-  <si>
-    <t>There is only one mode. In some corner cases, a resource may be included because it is both a match and an include. In these circumstances, 'match' takes precedence.</t>
-  </si>
-  <si>
-    <t>Why an entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/search-entry-mode|4.0.1</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
-    <t>Search ranking (between 0 and 1)</t>
-  </si>
-  <si>
-    <t>When searching, the server's search ranking score for the entry.</t>
-  </si>
-  <si>
-    <t>Servers are not required to return a ranking score. 1 is most relevant, and 0 is least relevant. Often, search results are sorted by score, but the client may specify a different sort order.
-See [Patient Match](http://hl7.org/fhir/R4/patient-operation-match.html) for the EMPI search which relates to this element.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request</t>
-  </si>
-  <si>
-    <t>Additional execution information (transaction/batch/history)</t>
-  </si>
-  <si>
-    <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
-  </si>
-  <si>
-    <t>ele-1
-bdl-3</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.method</t>
-  </si>
-  <si>
-    <t>GET | HEAD | POST | PUT | DELETE | PATCH</t>
-  </si>
-  <si>
-    <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
+    <t>Bundle.entry:DUIDocumentReference.search</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.search.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.search.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.search.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.search.mode</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.search.score</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.request</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.request.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.request.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.request.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.request.method</t>
   </si>
   <si>
     <t>POST</t>
   </si>
   <si>
-    <t>HTTP verbs (in the HTTP command line). See [HTTP rfc](https://tools.ietf.org/html/rfc7231) for details.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/http-verb|4.0.1</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.url</t>
-  </si>
-  <si>
-    <t>URL for HTTP equivalent of this entry</t>
-  </si>
-  <si>
-    <t>The URL for this entry, relative to the root (the address to which the request is posted).</t>
-  </si>
-  <si>
-    <t>E.g. for a Patient Create, the method would be "POST" and the URL would be "Patient". For a Patient Update, the method would be PUT and the URL would be "Patient/[id]".</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifNoneMatch</t>
-  </si>
-  <si>
-    <t>For managing cache currency</t>
-  </si>
-  <si>
-    <t>If the ETag values match, return a 304 Not Modified status. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifModifiedSince</t>
-  </si>
-  <si>
-    <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
-  </si>
-  <si>
-    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifMatch</t>
-  </si>
-  <si>
-    <t>For managing update contention</t>
-  </si>
-  <si>
-    <t>Only perform the operation if the Etag value matches. For more information, see the API section ["Managing Resource Contention"](http://hl7.org/fhir/R4/http.html#concurrency).</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifNoneExist</t>
-  </si>
-  <si>
-    <t>For conditional creates</t>
-  </si>
-  <si>
-    <t>Instruct the server not to perform the create if a specified resource already exists. For further information, see the API documentation for ["Conditional Create"](http://hl7.org/fhir/R4/http.html#ccreate). This is just the query portion of the URL - what follows the "?" (not including the "?").</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response</t>
-  </si>
-  <si>
-    <t>Results of execution (transaction/batch/history)</t>
-  </si>
-  <si>
-    <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
-  </si>
-  <si>
-    <t>ele-1
-bdl-4</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.status</t>
-  </si>
-  <si>
-    <t>Status response code (text optional)</t>
-  </si>
-  <si>
-    <t>The status code returned by processing this entry. The status SHALL start with a 3 digit HTTP code (e.g. 404) and may contain the standard HTTP description associated with the status code.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.location</t>
-  </si>
-  <si>
-    <t>The location (if the operation returns a location)</t>
-  </si>
-  <si>
-    <t>The location header created by processing this operation, populated if the operation returns a location.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.etag</t>
-  </si>
-  <si>
-    <t>The Etag for the resource (if relevant)</t>
-  </si>
-  <si>
-    <t>The Etag for the resource, if the operation for the entry produced a versioned resource (see [Resource Metadata and Versioning](http://hl7.org/fhir/R4/http.html#versioning) and [Managing Resource Contention](http://hl7.org/fhir/R4/http.html#concurrency)).</t>
-  </si>
-  <si>
-    <t>Etags match the Resource.meta.versionId. The ETag has to match the version id in the header if a resource is included.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.lastModified</t>
-  </si>
-  <si>
-    <t>Server's date time modified</t>
-  </si>
-  <si>
-    <t>The date/time that the resource was modified on the server.</t>
-  </si>
-  <si>
-    <t>This has to match the same time in the meta header (meta.lastUpdated) if a resource is included.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.outcome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>OperationOutcome with hints and warnings (for batch/transaction)</t>
-  </si>
-  <si>
-    <t>An OperationOutcome containing hints and warnings produced as part of processing this entry in a batch or transaction.</t>
-  </si>
-  <si>
-    <t>For a POST/PUT operation, this is the equivalent outcome that would be returned for prefer = operationoutcome - except that the resource is always returned whether or not the outcome is returned.
-This outcome is not used for error responses in batch/transaction, only for hints and warnings. In a batch operation, the error will be in Bundle.entry.response, and for transaction, there will be a single OperationOutcome instead of a bundle in the case of an error.</t>
+    <t>Bundle.entry:DUIDocumentReference.request.url</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.request.ifNoneMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.request.ifModifiedSince</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.request.ifMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.request.ifNoneExist</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.response</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.response.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.response.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.response.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.response.status</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.response.location</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.response.etag</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.response.lastModified</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.response.outcome</t>
   </si>
   <si>
     <t>Bundle.signature</t>
@@ -1948,7 +2063,7 @@
         <v>2</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
     </row>
     <row r="23">
@@ -1956,7 +2071,7 @@
         <v>4</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24">
@@ -1972,7 +2087,7 @@
         <v>8</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>234</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26">
@@ -1980,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>235</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27">
@@ -2026,7 +2141,7 @@
         <v>21</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>236</v>
+        <v>274</v>
       </c>
     </row>
     <row r="33">
@@ -2062,7 +2177,7 @@
         <v>29</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>237</v>
+        <v>275</v>
       </c>
     </row>
     <row r="38">
@@ -2070,7 +2185,7 @@
         <v>31</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>238</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39">
@@ -2096,12 +2211,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK111"/>
+  <dimension ref="A1:AK143"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="24.5078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="50.828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="61.7734375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="50.828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="23.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="39.9140625" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="2.2109375" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="2.2109375" customWidth="true" bestFit="true"/>
@@ -2124,13 +2240,12 @@
     <col min="26" max="26" width="168.19140625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="120.0625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="10.26171875" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="42.03515625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="16.66796875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="50.03125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="1.04296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="5.62109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="44.0703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="2.2109375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" hidden="true" width="8.0" customWidth="false"/>
     <col min="18" max="18" width="20.703125" customWidth="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
   </cols>
@@ -3782,16 +3897,16 @@
         <v>37</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="AD16" t="s" s="2">
-        <v>37</v>
+        <v>137</v>
       </c>
       <c r="AE16" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>133</v>
@@ -3806,7 +3921,7 @@
         <v>57</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17">
@@ -3814,10 +3929,10 @@
         <v>3</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
@@ -3917,10 +4032,10 @@
         <v>3</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
@@ -4022,10 +4137,10 @@
         <v>3</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
@@ -4129,10 +4244,10 @@
         <v>3</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
@@ -4158,10 +4273,10 @@
         <v>40</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -4212,7 +4327,7 @@
         <v>37</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>38</v>
@@ -4232,10 +4347,10 @@
         <v>3</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -4261,13 +4376,13 @@
         <v>60</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P21" s="2"/>
       <c r="Q21" t="s" s="2">
@@ -4317,7 +4432,7 @@
         <v>37</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>38</v>
@@ -4337,10 +4452,10 @@
         <v>3</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -4348,7 +4463,7 @@
       </c>
       <c r="F22" s="2"/>
       <c r="G22" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>45</v>
@@ -4360,20 +4475,18 @@
         <v>37</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" s="2"/>
       <c r="Q22" t="s" s="2">
         <v>37</v>
@@ -4422,7 +4535,7 @@
         <v>37</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>38</v>
@@ -4434,7 +4547,7 @@
         <v>37</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>152</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -5534,7 +5647,7 @@
         <v>37</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>181</v>
+        <v>37</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>37</v>
@@ -5552,10 +5665,10 @@
         <v>84</v>
       </c>
       <c r="Z33" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AA33" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AB33" t="s" s="2">
         <v>37</v>
@@ -5593,10 +5706,10 @@
         <v>3</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -5622,13 +5735,13 @@
         <v>60</v>
       </c>
       <c r="M34" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="P34" s="2"/>
       <c r="Q34" t="s" s="2">
@@ -5678,7 +5791,7 @@
         <v>37</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>45</v>
@@ -5698,10 +5811,10 @@
         <v>3</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -5727,10 +5840,10 @@
         <v>104</v>
       </c>
       <c r="M35" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="O35" t="s" s="2">
         <v>128</v>
@@ -5783,7 +5896,7 @@
         <v>37</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>38</v>
@@ -5803,10 +5916,10 @@
         <v>3</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -5832,13 +5945,13 @@
         <v>88</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N36" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="O36" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="P36" s="2"/>
       <c r="Q36" t="s" s="2">
@@ -5888,7 +6001,7 @@
         <v>37</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>38</v>
@@ -5908,10 +6021,10 @@
         <v>3</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -5937,10 +6050,10 @@
         <v>104</v>
       </c>
       <c r="M37" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="O37" t="s" s="2">
         <v>128</v>
@@ -5993,7 +6106,7 @@
         <v>37</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>38</v>
@@ -6013,10 +6126,10 @@
         <v>3</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -6042,10 +6155,10 @@
         <v>104</v>
       </c>
       <c r="M38" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>128</v>
@@ -6098,7 +6211,7 @@
         <v>37</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>38</v>
@@ -6118,10 +6231,10 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6147,10 +6260,10 @@
         <v>99</v>
       </c>
       <c r="M39" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
@@ -6201,7 +6314,7 @@
         <v>37</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>38</v>
@@ -6210,7 +6323,7 @@
         <v>45</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>58</v>
@@ -6221,10 +6334,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6324,10 +6437,10 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -6429,10 +6542,10 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -6536,10 +6649,10 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -6565,10 +6678,10 @@
         <v>104</v>
       </c>
       <c r="M43" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="O43" t="s" s="2">
         <v>128</v>
@@ -6621,7 +6734,7 @@
         <v>37</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>45</v>
@@ -6641,10 +6754,10 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
@@ -6670,10 +6783,10 @@
         <v>60</v>
       </c>
       <c r="M44" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="O44" t="s" s="2">
         <v>132</v>
@@ -6726,7 +6839,7 @@
         <v>37</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>38</v>
@@ -6746,10 +6859,10 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -6775,13 +6888,13 @@
         <v>104</v>
       </c>
       <c r="M45" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="P45" s="2"/>
       <c r="Q45" t="s" s="2">
@@ -6831,7 +6944,7 @@
         <v>37</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>38</v>
@@ -6851,10 +6964,10 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -6880,13 +6993,13 @@
         <v>88</v>
       </c>
       <c r="M46" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P46" s="2"/>
       <c r="Q46" t="s" s="2">
@@ -6936,7 +7049,7 @@
         <v>37</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>38</v>
@@ -6956,10 +7069,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -6982,16 +7095,16 @@
         <v>46</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="P47" s="2"/>
       <c r="Q47" t="s" s="2">
@@ -7041,7 +7154,7 @@
         <v>37</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>38</v>
@@ -7061,18 +7174,20 @@
         <v>3</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="D48" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="D48" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="E48" t="s" s="2">
         <v>37</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>45</v>
@@ -7087,20 +7202,16 @@
         <v>46</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="P48" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="O48" s="2"/>
+      <c r="P48" s="2"/>
       <c r="Q48" t="s" s="2">
         <v>37</v>
       </c>
@@ -7148,30 +7259,30 @@
         <v>37</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>226</v>
+        <v>133</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>58</v>
+        <v>138</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>237</v>
+        <v>139</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -7182,7 +7293,7 @@
         <v>38</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>37</v>
@@ -7194,17 +7305,15 @@
         <v>37</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>149</v>
+        <v>105</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" s="2"/>
       <c r="Q49" t="s" s="2">
         <v>37</v>
@@ -7253,41 +7362,41 @@
         <v>37</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>152</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>239</v>
+        <v>140</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>37</v>
@@ -7296,19 +7405,19 @@
         <v>37</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>48</v>
+        <v>111</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>50</v>
+        <v>113</v>
       </c>
       <c r="P50" s="2"/>
       <c r="Q50" t="s" s="2">
@@ -7346,74 +7455,78 @@
         <v>37</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="AD50" t="s" s="2">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="AE50" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>37</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>240</v>
+        <v>141</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>46</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="O51" s="2"/>
-      <c r="P51" s="2"/>
+        <v>122</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>123</v>
+      </c>
       <c r="Q51" t="s" s="2">
         <v>37</v>
       </c>
@@ -7461,30 +7574,30 @@
         <v>37</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>58</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>241</v>
+        <v>142</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -7495,7 +7608,7 @@
         <v>38</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>37</v>
@@ -7504,16 +7617,16 @@
         <v>37</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
@@ -7564,13 +7677,13 @@
         <v>37</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>37</v>
@@ -7581,24 +7694,24 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>242</v>
+        <v>145</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>37</v>
@@ -7607,19 +7720,19 @@
         <v>37</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="P53" s="2"/>
       <c r="Q53" t="s" s="2">
@@ -7657,42 +7770,42 @@
         <v>37</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="AD53" t="s" s="2">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="AE53" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>118</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="B54" t="s" s="2">
-        <v>243</v>
-      </c>
       <c r="C54" t="s" s="2">
-        <v>243</v>
+        <v>149</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -7700,31 +7813,31 @@
       </c>
       <c r="F54" s="2"/>
       <c r="G54" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>45</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>37</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>47</v>
+        <v>233</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="P54" s="2"/>
       <c r="Q54" t="s" s="2">
@@ -7774,7 +7887,7 @@
         <v>37</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>247</v>
+        <v>149</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>38</v>
@@ -7783,21 +7896,21 @@
         <v>45</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>58</v>
+        <v>237</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>248</v>
+        <v>153</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -7820,17 +7933,15 @@
         <v>46</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>249</v>
+        <v>154</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" s="2"/>
       <c r="Q55" t="s" s="2">
         <v>37</v>
@@ -7879,7 +7990,7 @@
         <v>37</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>252</v>
+        <v>153</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>38</v>
@@ -7888,7 +7999,7 @@
         <v>45</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>57</v>
+        <v>156</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>58</v>
@@ -7896,13 +8007,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>253</v>
+        <v>157</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -7922,20 +8033,18 @@
         <v>37</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" s="2"/>
       <c r="Q56" t="s" s="2">
         <v>37</v>
@@ -7984,7 +8093,7 @@
         <v>37</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>257</v>
+        <v>107</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>38</v>
@@ -7993,25 +8102,25 @@
         <v>45</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>258</v>
+        <v>158</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" t="s" s="2">
@@ -8027,19 +8136,19 @@
         <v>37</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>259</v>
+        <v>110</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>260</v>
+        <v>111</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>261</v>
+        <v>112</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>262</v>
+        <v>113</v>
       </c>
       <c r="P57" s="2"/>
       <c r="Q57" t="s" s="2">
@@ -8077,19 +8186,19 @@
         <v>37</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="AD57" t="s" s="2">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="AE57" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>263</v>
+        <v>117</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>38</v>
@@ -8101,22 +8210,22 @@
         <v>57</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>58</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>264</v>
+        <v>159</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" t="s" s="2">
@@ -8129,24 +8238,26 @@
         <v>37</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>46</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>265</v>
+        <v>110</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>266</v>
+        <v>121</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>267</v>
+        <v>122</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="P58" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>123</v>
+      </c>
       <c r="Q58" t="s" s="2">
         <v>37</v>
       </c>
@@ -8170,13 +8281,13 @@
         <v>37</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>269</v>
+        <v>37</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>270</v>
+        <v>37</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>271</v>
+        <v>37</v>
       </c>
       <c r="AB58" t="s" s="2">
         <v>37</v>
@@ -8194,7 +8305,7 @@
         <v>37</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>272</v>
+        <v>124</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>38</v>
@@ -8206,18 +8317,18 @@
         <v>57</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>58</v>
+        <v>118</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>273</v>
+        <v>242</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>273</v>
+        <v>160</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -8228,7 +8339,7 @@
         <v>38</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>37</v>
@@ -8240,16 +8351,16 @@
         <v>46</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>265</v>
+        <v>66</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>274</v>
+        <v>161</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>275</v>
+        <v>162</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>276</v>
+        <v>163</v>
       </c>
       <c r="P59" s="2"/>
       <c r="Q59" t="s" s="2">
@@ -8275,13 +8386,13 @@
         <v>37</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>277</v>
+        <v>84</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>278</v>
+        <v>164</v>
       </c>
       <c r="AA59" t="s" s="2">
-        <v>279</v>
+        <v>165</v>
       </c>
       <c r="AB59" t="s" s="2">
         <v>37</v>
@@ -8299,13 +8410,13 @@
         <v>37</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>280</v>
+        <v>160</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>57</v>
@@ -8316,13 +8427,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>281</v>
+        <v>243</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>281</v>
+        <v>166</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -8339,22 +8450,22 @@
         <v>37</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>46</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>60</v>
+        <v>167</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>61</v>
+        <v>168</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>62</v>
+        <v>169</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>63</v>
+        <v>170</v>
       </c>
       <c r="P60" s="2"/>
       <c r="Q60" t="s" s="2">
@@ -8404,7 +8515,7 @@
         <v>37</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>64</v>
+        <v>166</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>38</v>
@@ -8421,13 +8532,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>282</v>
+        <v>244</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>282</v>
+        <v>171</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -8435,7 +8546,7 @@
       </c>
       <c r="F61" s="2"/>
       <c r="G61" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>45</v>
@@ -8447,20 +8558,18 @@
         <v>37</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>67</v>
+        <v>172</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>69</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" s="2"/>
       <c r="Q61" t="s" s="2">
         <v>37</v>
@@ -8485,13 +8594,13 @@
         <v>37</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="AA61" t="s" s="2">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="AB61" t="s" s="2">
         <v>37</v>
@@ -8509,7 +8618,7 @@
         <v>37</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>38</v>
@@ -8518,7 +8627,7 @@
         <v>45</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>57</v>
+        <v>174</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>58</v>
@@ -8526,17 +8635,17 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>283</v>
+        <v>245</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>283</v>
+        <v>175</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
-        <v>284</v>
+        <v>37</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" t="s" s="2">
@@ -8555,17 +8664,15 @@
         <v>37</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>285</v>
+        <v>104</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>286</v>
+        <v>105</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" s="2"/>
       <c r="Q62" t="s" s="2">
         <v>37</v>
@@ -8614,7 +8721,7 @@
         <v>37</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>289</v>
+        <v>107</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>38</v>
@@ -8623,25 +8730,25 @@
         <v>45</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>290</v>
+        <v>246</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>290</v>
+        <v>176</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
-        <v>291</v>
+        <v>109</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" t="s" s="2">
@@ -8660,16 +8767,16 @@
         <v>37</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>222</v>
+        <v>110</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>292</v>
+        <v>111</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>293</v>
+        <v>112</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>294</v>
+        <v>113</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" t="s" s="2">
@@ -8707,19 +8814,19 @@
         <v>37</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="AD63" t="s" s="2">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="AE63" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>295</v>
+        <v>117</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>38</v>
@@ -8728,25 +8835,25 @@
         <v>39</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>37</v>
+        <v>118</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>296</v>
+        <v>177</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" t="s" s="2">
@@ -8759,24 +8866,26 @@
         <v>37</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>110</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>297</v>
+        <v>122</v>
       </c>
       <c r="O64" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="P64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>123</v>
+      </c>
       <c r="Q64" t="s" s="2">
         <v>37</v>
       </c>
@@ -8812,19 +8921,19 @@
         <v>37</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="AD64" t="s" s="2">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="AE64" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>298</v>
+        <v>124</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>38</v>
@@ -8841,13 +8950,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>299</v>
+        <v>248</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>299</v>
+        <v>178</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -8855,30 +8964,32 @@
       </c>
       <c r="F65" s="2"/>
       <c r="G65" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J65" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K65" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="K65" t="s" s="2">
-        <v>37</v>
-      </c>
       <c r="L65" t="s" s="2">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>300</v>
+        <v>179</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>128</v>
+      </c>
       <c r="P65" s="2"/>
       <c r="Q65" t="s" s="2">
         <v>37</v>
@@ -8888,7 +8999,7 @@
         <v>37</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>37</v>
+        <v>249</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>37</v>
@@ -8903,54 +9014,54 @@
         <v>37</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>37</v>
+        <v>181</v>
       </c>
       <c r="AA65" t="s" s="2">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="AB65" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="AD65" t="s" s="2">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="AE65" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>302</v>
+        <v>178</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>118</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>303</v>
+        <v>250</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>303</v>
+        <v>183</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -8964,7 +9075,7 @@
         <v>45</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>37</v>
@@ -8973,20 +9084,18 @@
         <v>46</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>304</v>
+        <v>184</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>305</v>
+        <v>185</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="P66" s="2"/>
       <c r="Q66" t="s" s="2">
         <v>37</v>
       </c>
@@ -9034,10 +9143,10 @@
         <v>37</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>303</v>
+        <v>183</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>45</v>
@@ -9051,13 +9160,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>308</v>
+        <v>251</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>308</v>
+        <v>187</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -9068,10 +9177,10 @@
         <v>38</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>37</v>
@@ -9080,15 +9189,17 @@
         <v>46</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>309</v>
+        <v>188</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>128</v>
+      </c>
       <c r="P67" s="2"/>
       <c r="Q67" t="s" s="2">
         <v>37</v>
@@ -9137,13 +9248,13 @@
         <v>37</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>308</v>
+        <v>187</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>57</v>
@@ -9154,13 +9265,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>311</v>
+        <v>252</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>311</v>
+        <v>190</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -9168,31 +9279,31 @@
       </c>
       <c r="F68" s="2"/>
       <c r="G68" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>45</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>46</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>312</v>
+        <v>188</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>313</v>
+        <v>191</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>314</v>
+        <v>192</v>
       </c>
       <c r="P68" s="2"/>
       <c r="Q68" t="s" s="2">
@@ -9203,7 +9314,7 @@
         <v>37</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>315</v>
+        <v>37</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>37</v>
@@ -9218,13 +9329,13 @@
         <v>37</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>316</v>
+        <v>37</v>
       </c>
       <c r="AA68" t="s" s="2">
-        <v>317</v>
+        <v>37</v>
       </c>
       <c r="AB68" t="s" s="2">
         <v>37</v>
@@ -9242,10 +9353,10 @@
         <v>37</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>311</v>
+        <v>190</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>45</v>
@@ -9259,13 +9370,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>318</v>
+        <v>253</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>318</v>
+        <v>193</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -9276,7 +9387,7 @@
         <v>38</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>37</v>
@@ -9288,16 +9399,16 @@
         <v>46</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>319</v>
+        <v>194</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>320</v>
+        <v>195</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>321</v>
+        <v>128</v>
       </c>
       <c r="P69" s="2"/>
       <c r="Q69" t="s" s="2">
@@ -9323,13 +9434,13 @@
         <v>37</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>322</v>
+        <v>37</v>
       </c>
       <c r="AA69" t="s" s="2">
-        <v>323</v>
+        <v>37</v>
       </c>
       <c r="AB69" t="s" s="2">
         <v>37</v>
@@ -9347,7 +9458,7 @@
         <v>37</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>318</v>
+        <v>193</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>38</v>
@@ -9364,13 +9475,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>324</v>
+        <v>254</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>324</v>
+        <v>196</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -9384,7 +9495,7 @@
         <v>45</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J70" t="s" s="2">
         <v>37</v>
@@ -9393,16 +9504,16 @@
         <v>46</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>325</v>
+        <v>104</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>326</v>
+        <v>197</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>327</v>
+        <v>198</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>328</v>
+        <v>128</v>
       </c>
       <c r="P70" s="2"/>
       <c r="Q70" t="s" s="2">
@@ -9428,11 +9539,13 @@
         <v>37</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="Z70" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>37</v>
+      </c>
       <c r="AA70" t="s" s="2">
-        <v>329</v>
+        <v>37</v>
       </c>
       <c r="AB70" t="s" s="2">
         <v>37</v>
@@ -9450,7 +9563,7 @@
         <v>37</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>324</v>
+        <v>196</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>38</v>
@@ -9462,22 +9575,22 @@
         <v>57</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>330</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>331</v>
+        <v>255</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>331</v>
+        <v>199</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
-        <v>332</v>
+        <v>37</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" t="s" s="2">
@@ -9487,7 +9600,7 @@
         <v>45</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J71" t="s" s="2">
         <v>37</v>
@@ -9496,17 +9609,15 @@
         <v>46</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>325</v>
+        <v>99</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>333</v>
+        <v>200</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" s="2"/>
       <c r="Q71" t="s" s="2">
         <v>37</v>
@@ -9531,11 +9642,13 @@
         <v>37</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="Z71" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>37</v>
+      </c>
       <c r="AA71" t="s" s="2">
-        <v>336</v>
+        <v>37</v>
       </c>
       <c r="AB71" t="s" s="2">
         <v>37</v>
@@ -9553,30 +9666,30 @@
         <v>37</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>331</v>
+        <v>199</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>57</v>
+        <v>202</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>337</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>338</v>
+        <v>256</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>338</v>
+        <v>203</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -9596,20 +9709,18 @@
         <v>37</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>339</v>
+        <v>104</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>340</v>
+        <v>105</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" s="2"/>
       <c r="Q72" t="s" s="2">
         <v>37</v>
@@ -9658,7 +9769,7 @@
         <v>37</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>338</v>
+        <v>107</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>38</v>
@@ -9667,53 +9778,53 @@
         <v>45</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>343</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>344</v>
+        <v>257</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>344</v>
+        <v>204</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
-        <v>345</v>
+        <v>109</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J73" t="s" s="2">
         <v>37</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>346</v>
+        <v>111</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>347</v>
+        <v>112</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>348</v>
+        <v>113</v>
       </c>
       <c r="P73" s="2"/>
       <c r="Q73" t="s" s="2">
@@ -9751,46 +9862,46 @@
         <v>37</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="AD73" t="s" s="2">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="AE73" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>344</v>
+        <v>117</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>58</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>349</v>
+        <v>258</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>349</v>
+        <v>205</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" t="s" s="2">
@@ -9800,27 +9911,29 @@
         <v>39</v>
       </c>
       <c r="I74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J74" t="s" s="2">
         <v>46</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>37</v>
       </c>
       <c r="K74" t="s" s="2">
         <v>46</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>350</v>
+        <v>110</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>351</v>
+        <v>121</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>352</v>
+        <v>122</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="P74" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>123</v>
+      </c>
       <c r="Q74" t="s" s="2">
         <v>37</v>
       </c>
@@ -9868,7 +9981,7 @@
         <v>37</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>349</v>
+        <v>124</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>38</v>
@@ -9880,18 +9993,18 @@
         <v>57</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>343</v>
+        <v>118</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>354</v>
+        <v>259</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>354</v>
+        <v>206</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -9899,31 +10012,31 @@
       </c>
       <c r="F75" s="2"/>
       <c r="G75" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>45</v>
       </c>
       <c r="I75" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K75" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="J75" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>37</v>
-      </c>
       <c r="L75" t="s" s="2">
-        <v>355</v>
+        <v>104</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>356</v>
+        <v>207</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>357</v>
+        <v>208</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>358</v>
+        <v>128</v>
       </c>
       <c r="P75" s="2"/>
       <c r="Q75" t="s" s="2">
@@ -9973,10 +10086,10 @@
         <v>37</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>354</v>
+        <v>206</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>45</v>
@@ -9985,18 +10098,18 @@
         <v>57</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>343</v>
+        <v>58</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>359</v>
+        <v>260</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>359</v>
+        <v>209</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10016,19 +10129,19 @@
         <v>37</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>360</v>
+        <v>60</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>361</v>
+        <v>210</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>362</v>
+        <v>211</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>363</v>
+        <v>132</v>
       </c>
       <c r="P76" s="2"/>
       <c r="Q76" t="s" s="2">
@@ -10078,7 +10191,7 @@
         <v>37</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>359</v>
+        <v>209</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>38</v>
@@ -10090,18 +10203,18 @@
         <v>57</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>343</v>
+        <v>58</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>364</v>
+        <v>261</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>364</v>
+        <v>212</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -10112,10 +10225,10 @@
         <v>38</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>37</v>
@@ -10124,16 +10237,16 @@
         <v>46</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>365</v>
+        <v>213</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>366</v>
+        <v>214</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>367</v>
+        <v>215</v>
       </c>
       <c r="P77" s="2"/>
       <c r="Q77" t="s" s="2">
@@ -10183,13 +10296,13 @@
         <v>37</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>364</v>
+        <v>212</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>57</v>
@@ -10200,13 +10313,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>368</v>
+        <v>262</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>368</v>
+        <v>216</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -10226,18 +10339,20 @@
         <v>37</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>105</v>
+        <v>217</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="P78" s="2"/>
       <c r="Q78" t="s" s="2">
         <v>37</v>
@@ -10286,7 +10401,7 @@
         <v>37</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>107</v>
+        <v>216</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>38</v>
@@ -10295,32 +10410,32 @@
         <v>45</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>369</v>
+        <v>263</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>369</v>
+        <v>220</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>37</v>
@@ -10329,19 +10444,19 @@
         <v>37</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>111</v>
+        <v>221</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>112</v>
+        <v>222</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>113</v>
+        <v>223</v>
       </c>
       <c r="P79" s="2"/>
       <c r="Q79" t="s" s="2">
@@ -10379,77 +10494,77 @@
         <v>37</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="AD79" t="s" s="2">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="AE79" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>117</v>
+        <v>220</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>118</v>
+        <v>37</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>370</v>
+        <v>264</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>370</v>
+        <v>264</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>46</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>110</v>
+        <v>265</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>121</v>
+        <v>266</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>122</v>
+        <v>267</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>113</v>
+        <v>268</v>
       </c>
       <c r="P80" t="s" s="2">
-        <v>123</v>
+        <v>269</v>
       </c>
       <c r="Q80" t="s" s="2">
         <v>37</v>
@@ -10498,30 +10613,30 @@
         <v>37</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>124</v>
+        <v>264</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>118</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>371</v>
+        <v>275</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>371</v>
+        <v>275</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -10529,10 +10644,10 @@
       </c>
       <c r="F81" s="2"/>
       <c r="G81" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>37</v>
@@ -10541,19 +10656,19 @@
         <v>37</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>372</v>
+        <v>234</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>373</v>
+        <v>235</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>374</v>
+        <v>236</v>
       </c>
       <c r="P81" s="2"/>
       <c r="Q81" t="s" s="2">
@@ -10579,13 +10694,13 @@
         <v>37</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>375</v>
+        <v>37</v>
       </c>
       <c r="AA81" t="s" s="2">
-        <v>376</v>
+        <v>37</v>
       </c>
       <c r="AB81" t="s" s="2">
         <v>37</v>
@@ -10603,30 +10718,30 @@
         <v>37</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>371</v>
+        <v>275</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>58</v>
+        <v>237</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>377</v>
+        <v>277</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>377</v>
+        <v>277</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -10634,7 +10749,7 @@
       </c>
       <c r="F82" s="2"/>
       <c r="G82" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>45</v>
@@ -10649,16 +10764,16 @@
         <v>46</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>378</v>
+        <v>47</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>379</v>
+        <v>48</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>380</v>
+        <v>49</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>342</v>
+        <v>50</v>
       </c>
       <c r="P82" s="2"/>
       <c r="Q82" t="s" s="2">
@@ -10708,30 +10823,30 @@
         <v>37</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>377</v>
+        <v>51</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>45</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>343</v>
+        <v>37</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>381</v>
+        <v>278</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>381</v>
+        <v>278</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -10745,7 +10860,7 @@
         <v>45</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>37</v>
@@ -10754,20 +10869,16 @@
         <v>46</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>382</v>
+        <v>54</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" s="2"/>
       <c r="Q83" t="s" s="2">
         <v>37</v>
       </c>
@@ -10815,7 +10926,7 @@
         <v>37</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>381</v>
+        <v>56</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>38</v>
@@ -10832,13 +10943,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>386</v>
+        <v>279</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>386</v>
+        <v>279</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -10849,32 +10960,28 @@
         <v>38</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J84" t="s" s="2">
         <v>37</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>325</v>
+        <v>104</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>387</v>
+        <v>105</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O84" s="2"/>
+      <c r="P84" s="2"/>
       <c r="Q84" t="s" s="2">
         <v>37</v>
       </c>
@@ -10898,13 +11005,13 @@
         <v>37</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>269</v>
+        <v>37</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>270</v>
+        <v>37</v>
       </c>
       <c r="AA84" t="s" s="2">
-        <v>271</v>
+        <v>37</v>
       </c>
       <c r="AB84" t="s" s="2">
         <v>37</v>
@@ -10922,61 +11029,63 @@
         <v>37</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>386</v>
+        <v>107</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>391</v>
+        <v>37</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>392</v>
+        <v>280</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>392</v>
+        <v>280</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J85" t="s" s="2">
         <v>37</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>393</v>
+        <v>111</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="P85" s="2"/>
       <c r="Q85" t="s" s="2">
         <v>37</v>
@@ -11013,22 +11122,22 @@
         <v>37</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="AD85" t="s" s="2">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="AE85" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>392</v>
+        <v>117</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>39</v>
@@ -11037,18 +11146,18 @@
         <v>57</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>58</v>
+        <v>118</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>395</v>
+        <v>281</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>395</v>
+        <v>281</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -11062,24 +11171,26 @@
         <v>45</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J86" t="s" s="2">
         <v>37</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>105</v>
+        <v>282</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O86" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P86" s="2"/>
       <c r="Q86" t="s" s="2">
         <v>37</v>
@@ -11128,7 +11239,7 @@
         <v>37</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>107</v>
+        <v>285</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>38</v>
@@ -11137,32 +11248,32 @@
         <v>45</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>396</v>
+        <v>286</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>396</v>
+        <v>286</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>37</v>
@@ -11171,19 +11282,19 @@
         <v>37</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>111</v>
+        <v>287</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>112</v>
+        <v>288</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>113</v>
+        <v>289</v>
       </c>
       <c r="P87" s="2"/>
       <c r="Q87" t="s" s="2">
@@ -11221,78 +11332,76 @@
         <v>37</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="AD87" t="s" s="2">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="AE87" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>117</v>
+        <v>290</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>118</v>
+        <v>58</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>397</v>
+        <v>291</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>397</v>
+        <v>291</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K88" t="s" s="2">
         <v>46</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>121</v>
+        <v>292</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>122</v>
+        <v>293</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>123</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="P88" s="2"/>
       <c r="Q88" t="s" s="2">
         <v>37</v>
       </c>
@@ -11340,30 +11449,30 @@
         <v>37</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>124</v>
+        <v>295</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>118</v>
+        <v>58</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>398</v>
+        <v>296</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>398</v>
+        <v>296</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -11371,10 +11480,10 @@
       </c>
       <c r="F89" s="2"/>
       <c r="G89" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>37</v>
@@ -11386,16 +11495,16 @@
         <v>46</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>399</v>
+        <v>297</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>400</v>
+        <v>298</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>401</v>
+        <v>299</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>402</v>
+        <v>300</v>
       </c>
       <c r="P89" s="2"/>
       <c r="Q89" t="s" s="2">
@@ -11445,30 +11554,30 @@
         <v>37</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>398</v>
+        <v>301</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>403</v>
+        <v>58</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>404</v>
+        <v>302</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>404</v>
+        <v>302</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -11479,7 +11588,7 @@
         <v>38</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>37</v>
@@ -11488,18 +11597,20 @@
         <v>37</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>104</v>
+        <v>303</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>105</v>
+        <v>304</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="P90" s="2"/>
       <c r="Q90" t="s" s="2">
         <v>37</v>
@@ -11524,13 +11635,13 @@
         <v>37</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>37</v>
+        <v>307</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>37</v>
+        <v>308</v>
       </c>
       <c r="AA90" t="s" s="2">
-        <v>37</v>
+        <v>309</v>
       </c>
       <c r="AB90" t="s" s="2">
         <v>37</v>
@@ -11548,34 +11659,34 @@
         <v>37</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>107</v>
+        <v>310</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>405</v>
+        <v>311</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>405</v>
+        <v>311</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="F91" s="2"/>
       <c r="G91" t="s" s="2">
@@ -11591,19 +11702,19 @@
         <v>37</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>110</v>
+        <v>303</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>111</v>
+        <v>312</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>112</v>
+        <v>313</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>113</v>
+        <v>314</v>
       </c>
       <c r="P91" s="2"/>
       <c r="Q91" t="s" s="2">
@@ -11629,31 +11740,31 @@
         <v>37</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>37</v>
+        <v>315</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>37</v>
+        <v>316</v>
       </c>
       <c r="AA91" t="s" s="2">
-        <v>37</v>
+        <v>317</v>
       </c>
       <c r="AB91" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="AD91" t="s" s="2">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="AE91" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>117</v>
+        <v>318</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>38</v>
@@ -11665,18 +11776,18 @@
         <v>57</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>118</v>
+        <v>58</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>406</v>
+        <v>319</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>406</v>
+        <v>319</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -11684,7 +11795,7 @@
       </c>
       <c r="F92" s="2"/>
       <c r="G92" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>45</v>
@@ -11693,26 +11804,24 @@
         <v>37</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K92" t="s" s="2">
         <v>46</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>407</v>
+        <v>61</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>408</v>
+        <v>62</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="P92" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="P92" s="2"/>
       <c r="Q92" t="s" s="2">
         <v>37</v>
       </c>
@@ -11724,7 +11833,7 @@
         <v>37</v>
       </c>
       <c r="U92" t="s" s="2">
-        <v>410</v>
+        <v>37</v>
       </c>
       <c r="V92" t="s" s="2">
         <v>37</v>
@@ -11736,13 +11845,13 @@
         <v>37</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>411</v>
+        <v>37</v>
       </c>
       <c r="AA92" t="s" s="2">
-        <v>412</v>
+        <v>37</v>
       </c>
       <c r="AB92" t="s" s="2">
         <v>37</v>
@@ -11760,7 +11869,7 @@
         <v>37</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>413</v>
+        <v>64</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>38</v>
@@ -11777,13 +11886,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>414</v>
+        <v>320</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>414</v>
+        <v>320</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -11797,29 +11906,27 @@
         <v>45</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J93" t="s" s="2">
         <v>37</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="L93" t="s" s="2">
         <v>66</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>415</v>
+        <v>67</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>416</v>
+        <v>68</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="P93" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="P93" s="2"/>
       <c r="Q93" t="s" s="2">
         <v>37</v>
       </c>
@@ -11831,7 +11938,7 @@
         <v>37</v>
       </c>
       <c r="U93" t="s" s="2">
-        <v>418</v>
+        <v>37</v>
       </c>
       <c r="V93" t="s" s="2">
         <v>37</v>
@@ -11867,7 +11974,7 @@
         <v>37</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>419</v>
+        <v>73</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>38</v>
@@ -11884,21 +11991,21 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>420</v>
+        <v>321</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>420</v>
+        <v>321</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
-        <v>37</v>
+        <v>322</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>45</v>
@@ -11913,20 +12020,18 @@
         <v>37</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>421</v>
+        <v>323</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>422</v>
+        <v>324</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>423</v>
+        <v>325</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="P94" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P94" s="2"/>
       <c r="Q94" t="s" s="2">
         <v>37</v>
       </c>
@@ -11974,7 +12079,7 @@
         <v>37</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>426</v>
+        <v>327</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>38</v>
@@ -11991,24 +12096,24 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>427</v>
+        <v>328</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>427</v>
+        <v>328</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
-        <v>37</v>
+        <v>329</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>37</v>
@@ -12017,23 +12122,21 @@
         <v>37</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>428</v>
+        <v>150</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>429</v>
+        <v>330</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>430</v>
+        <v>331</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="P95" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="P95" s="2"/>
       <c r="Q95" t="s" s="2">
         <v>37</v>
       </c>
@@ -12045,7 +12148,7 @@
         <v>37</v>
       </c>
       <c r="U95" t="s" s="2">
-        <v>433</v>
+        <v>37</v>
       </c>
       <c r="V95" t="s" s="2">
         <v>37</v>
@@ -12081,41 +12184,41 @@
         <v>37</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>434</v>
+        <v>333</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>435</v>
+        <v>334</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>435</v>
+        <v>334</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>37</v>
@@ -12124,23 +12227,21 @@
         <v>37</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>436</v>
+        <v>111</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>437</v>
+        <v>335</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="P96" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="P96" s="2"/>
       <c r="Q96" t="s" s="2">
         <v>37</v>
       </c>
@@ -12176,42 +12277,42 @@
         <v>37</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="AD96" t="s" s="2">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="AE96" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>440</v>
+        <v>336</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>58</v>
+        <v>118</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>441</v>
+        <v>337</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>441</v>
+        <v>337</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -12222,32 +12323,28 @@
         <v>38</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>421</v>
+        <v>110</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>442</v>
+        <v>338</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="P97" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="O97" s="2"/>
+      <c r="P97" s="2"/>
       <c r="Q97" t="s" s="2">
         <v>37</v>
       </c>
@@ -12283,42 +12380,42 @@
         <v>37</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="AD97" t="s" s="2">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="AE97" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>446</v>
+        <v>340</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>58</v>
+        <v>118</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>447</v>
+        <v>341</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>447</v>
+        <v>341</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -12332,7 +12429,7 @@
         <v>45</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J98" t="s" s="2">
         <v>37</v>
@@ -12341,19 +12438,19 @@
         <v>46</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>448</v>
+        <v>342</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>449</v>
+        <v>343</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>128</v>
+        <v>344</v>
       </c>
       <c r="P98" t="s" s="2">
-        <v>450</v>
+        <v>345</v>
       </c>
       <c r="Q98" t="s" s="2">
         <v>37</v>
@@ -12366,7 +12463,7 @@
         <v>37</v>
       </c>
       <c r="U98" t="s" s="2">
-        <v>451</v>
+        <v>37</v>
       </c>
       <c r="V98" t="s" s="2">
         <v>37</v>
@@ -12402,7 +12499,7 @@
         <v>37</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>452</v>
+        <v>341</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>38</v>
@@ -12419,13 +12516,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>453</v>
+        <v>346</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>453</v>
+        <v>346</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -12436,7 +12533,7 @@
         <v>38</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>46</v>
@@ -12448,18 +12545,16 @@
         <v>46</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>454</v>
+        <v>75</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>455</v>
+        <v>347</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>456</v>
+        <v>348</v>
       </c>
       <c r="O99" s="2"/>
-      <c r="P99" t="s" s="2">
-        <v>457</v>
-      </c>
+      <c r="P99" s="2"/>
       <c r="Q99" t="s" s="2">
         <v>37</v>
       </c>
@@ -12507,13 +12602,13 @@
         <v>37</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>458</v>
+        <v>346</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>57</v>
@@ -12524,13 +12619,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>459</v>
+        <v>349</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>459</v>
+        <v>349</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -12538,7 +12633,7 @@
       </c>
       <c r="F100" s="2"/>
       <c r="G100" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>45</v>
@@ -12547,22 +12642,22 @@
         <v>46</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K100" t="s" s="2">
         <v>46</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>265</v>
+        <v>66</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>460</v>
+        <v>350</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>461</v>
+        <v>351</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>462</v>
+        <v>352</v>
       </c>
       <c r="P100" s="2"/>
       <c r="Q100" t="s" s="2">
@@ -12573,7 +12668,7 @@
         <v>37</v>
       </c>
       <c r="T100" t="s" s="2">
-        <v>37</v>
+        <v>353</v>
       </c>
       <c r="U100" t="s" s="2">
         <v>37</v>
@@ -12588,11 +12683,13 @@
         <v>37</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="Z100" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="AA100" t="s" s="2">
-        <v>463</v>
+        <v>355</v>
       </c>
       <c r="AB100" t="s" s="2">
         <v>37</v>
@@ -12610,10 +12707,10 @@
         <v>37</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>459</v>
+        <v>349</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>45</v>
@@ -12622,18 +12719,18 @@
         <v>57</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>464</v>
+        <v>58</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>465</v>
+        <v>356</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>465</v>
+        <v>356</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -12644,10 +12741,10 @@
         <v>38</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J101" t="s" s="2">
         <v>37</v>
@@ -12656,16 +12753,16 @@
         <v>46</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>466</v>
+        <v>357</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>467</v>
+        <v>358</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>468</v>
+        <v>359</v>
       </c>
       <c r="P101" s="2"/>
       <c r="Q101" t="s" s="2">
@@ -12691,13 +12788,13 @@
         <v>37</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>37</v>
+        <v>360</v>
       </c>
       <c r="AA101" t="s" s="2">
-        <v>37</v>
+        <v>361</v>
       </c>
       <c r="AB101" t="s" s="2">
         <v>37</v>
@@ -12715,7 +12812,7 @@
         <v>37</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>465</v>
+        <v>356</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>38</v>
@@ -12732,13 +12829,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>469</v>
+        <v>362</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>469</v>
+        <v>362</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -12752,24 +12849,26 @@
         <v>45</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J102" t="s" s="2">
         <v>37</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>104</v>
+        <v>363</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>105</v>
+        <v>364</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O102" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="P102" s="2"/>
       <c r="Q102" t="s" s="2">
         <v>37</v>
@@ -12794,13 +12893,11 @@
         <v>37</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>37</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="Z102" s="2"/>
       <c r="AA102" t="s" s="2">
-        <v>37</v>
+        <v>367</v>
       </c>
       <c r="AB102" t="s" s="2">
         <v>37</v>
@@ -12818,7 +12915,7 @@
         <v>37</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>107</v>
+        <v>362</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>38</v>
@@ -12827,53 +12924,53 @@
         <v>45</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>37</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>470</v>
+        <v>369</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>470</v>
+        <v>369</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
-        <v>109</v>
+        <v>370</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J103" t="s" s="2">
         <v>37</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>110</v>
+        <v>363</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>111</v>
+        <v>371</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>112</v>
+        <v>372</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>113</v>
+        <v>373</v>
       </c>
       <c r="P103" s="2"/>
       <c r="Q103" t="s" s="2">
@@ -12899,31 +12996,29 @@
         <v>37</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>37</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="Z103" s="2"/>
       <c r="AA103" t="s" s="2">
-        <v>37</v>
+        <v>374</v>
       </c>
       <c r="AB103" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="AD103" t="s" s="2">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="AE103" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>117</v>
+        <v>369</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>38</v>
@@ -12935,54 +13030,52 @@
         <v>57</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>118</v>
+        <v>375</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>471</v>
+        <v>376</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>471</v>
+        <v>376</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K104" t="s" s="2">
         <v>46</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>110</v>
+        <v>377</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>121</v>
+        <v>378</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>122</v>
+        <v>379</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="P104" t="s" s="2">
-        <v>123</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="P104" s="2"/>
       <c r="Q104" t="s" s="2">
         <v>37</v>
       </c>
@@ -13030,62 +13123,62 @@
         <v>37</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>124</v>
+        <v>376</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>118</v>
+        <v>381</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>472</v>
+        <v>382</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>472</v>
+        <v>382</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
-        <v>37</v>
+        <v>383</v>
       </c>
       <c r="F105" s="2"/>
       <c r="G105" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J105" t="s" s="2">
         <v>37</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>473</v>
+        <v>88</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>474</v>
+        <v>384</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>475</v>
+        <v>385</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>342</v>
+        <v>386</v>
       </c>
       <c r="P105" s="2"/>
       <c r="Q105" t="s" s="2">
@@ -13135,30 +13228,30 @@
         <v>37</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>472</v>
+        <v>382</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>343</v>
+        <v>58</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>476</v>
+        <v>387</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>476</v>
+        <v>387</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -13169,28 +13262,28 @@
         <v>38</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>37</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>325</v>
+        <v>388</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>477</v>
+        <v>389</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>478</v>
+        <v>390</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>479</v>
+        <v>391</v>
       </c>
       <c r="P106" s="2"/>
       <c r="Q106" t="s" s="2">
@@ -13216,13 +13309,13 @@
         <v>37</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>277</v>
+        <v>37</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>480</v>
+        <v>37</v>
       </c>
       <c r="AA106" t="s" s="2">
-        <v>481</v>
+        <v>37</v>
       </c>
       <c r="AB106" t="s" s="2">
         <v>37</v>
@@ -13240,7 +13333,7 @@
         <v>37</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>476</v>
+        <v>387</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>38</v>
@@ -13252,18 +13345,18 @@
         <v>57</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>482</v>
+        <v>381</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>483</v>
+        <v>392</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>483</v>
+        <v>392</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -13283,19 +13376,19 @@
         <v>37</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>484</v>
+        <v>393</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>485</v>
+        <v>394</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>486</v>
+        <v>395</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>487</v>
+        <v>396</v>
       </c>
       <c r="P107" s="2"/>
       <c r="Q107" t="s" s="2">
@@ -13345,7 +13438,7 @@
         <v>37</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>483</v>
+        <v>392</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>38</v>
@@ -13357,18 +13450,18 @@
         <v>57</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>488</v>
+        <v>381</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>489</v>
+        <v>397</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>489</v>
+        <v>397</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -13382,7 +13475,7 @@
         <v>45</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J108" t="s" s="2">
         <v>37</v>
@@ -13391,16 +13484,16 @@
         <v>37</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>325</v>
+        <v>398</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>490</v>
+        <v>399</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>491</v>
+        <v>400</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>492</v>
+        <v>401</v>
       </c>
       <c r="P108" s="2"/>
       <c r="Q108" t="s" s="2">
@@ -13426,11 +13519,13 @@
         <v>37</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="Z108" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>37</v>
+      </c>
       <c r="AA108" t="s" s="2">
-        <v>493</v>
+        <v>37</v>
       </c>
       <c r="AB108" t="s" s="2">
         <v>37</v>
@@ -13448,7 +13543,7 @@
         <v>37</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>489</v>
+        <v>397</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>38</v>
@@ -13460,18 +13555,18 @@
         <v>57</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>494</v>
+        <v>381</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>495</v>
+        <v>402</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>495</v>
+        <v>402</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -13482,7 +13577,7 @@
         <v>38</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>46</v>
@@ -13491,23 +13586,21 @@
         <v>37</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>325</v>
+        <v>99</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>496</v>
+        <v>403</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>497</v>
+        <v>404</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="P109" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="P109" s="2"/>
       <c r="Q109" t="s" s="2">
         <v>37</v>
       </c>
@@ -13531,11 +13624,13 @@
         <v>37</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="Z109" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>37</v>
+      </c>
       <c r="AA109" t="s" s="2">
-        <v>500</v>
+        <v>37</v>
       </c>
       <c r="AB109" t="s" s="2">
         <v>37</v>
@@ -13553,30 +13648,30 @@
         <v>37</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>495</v>
+        <v>402</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>494</v>
+        <v>58</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>501</v>
+        <v>406</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>501</v>
+        <v>406</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -13590,7 +13685,7 @@
         <v>45</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J110" t="s" s="2">
         <v>37</v>
@@ -13599,17 +13694,15 @@
         <v>37</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>502</v>
+        <v>104</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>503</v>
+        <v>105</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O110" s="2"/>
       <c r="P110" s="2"/>
       <c r="Q110" t="s" s="2">
         <v>37</v>
@@ -13658,7 +13751,7 @@
         <v>37</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>501</v>
+        <v>107</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>38</v>
@@ -13667,25 +13760,25 @@
         <v>45</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>343</v>
+        <v>37</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>505</v>
+        <v>407</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>505</v>
+        <v>407</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" t="s" s="2">
@@ -13704,16 +13797,16 @@
         <v>37</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>506</v>
+        <v>110</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>507</v>
+        <v>111</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>508</v>
+        <v>112</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>509</v>
+        <v>113</v>
       </c>
       <c r="P111" s="2"/>
       <c r="Q111" t="s" s="2">
@@ -13751,19 +13844,19 @@
         <v>37</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="AD111" t="s" s="2">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="AE111" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>505</v>
+        <v>117</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>38</v>
@@ -13775,7 +13868,3379 @@
         <v>57</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>343</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="C112" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="D112" s="2"/>
+      <c r="E112" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="F112" s="2"/>
+      <c r="G112" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="P112" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="Q112" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R112" s="2"/>
+      <c r="S112" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="C113" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="D113" s="2"/>
+      <c r="E113" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F113" s="2"/>
+      <c r="G113" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="P113" s="2"/>
+      <c r="Q113" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R113" s="2"/>
+      <c r="S113" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="C114" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="D114" s="2"/>
+      <c r="E114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F114" s="2"/>
+      <c r="G114" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="P114" s="2"/>
+      <c r="Q114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R114" s="2"/>
+      <c r="S114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="D115" s="2"/>
+      <c r="E115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F115" s="2"/>
+      <c r="G115" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="P115" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="Q115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R115" s="2"/>
+      <c r="S115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="D116" s="2"/>
+      <c r="E116" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F116" s="2"/>
+      <c r="G116" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="P116" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="Q116" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R116" s="2"/>
+      <c r="S116" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="D117" s="2"/>
+      <c r="E117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F117" s="2"/>
+      <c r="G117" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="O117" s="2"/>
+      <c r="P117" s="2"/>
+      <c r="Q117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R117" s="2"/>
+      <c r="S117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="D118" s="2"/>
+      <c r="E118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F118" s="2"/>
+      <c r="G118" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O118" s="2"/>
+      <c r="P118" s="2"/>
+      <c r="Q118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R118" s="2"/>
+      <c r="S118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="D119" s="2"/>
+      <c r="E119" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="F119" s="2"/>
+      <c r="G119" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="P119" s="2"/>
+      <c r="Q119" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R119" s="2"/>
+      <c r="S119" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="D120" s="2"/>
+      <c r="E120" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="F120" s="2"/>
+      <c r="G120" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="P120" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="Q120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R120" s="2"/>
+      <c r="S120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="D121" s="2"/>
+      <c r="E121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F121" s="2"/>
+      <c r="G121" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="P121" s="2"/>
+      <c r="Q121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R121" s="2"/>
+      <c r="S121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="C122" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="D122" s="2"/>
+      <c r="E122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F122" s="2"/>
+      <c r="G122" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O122" s="2"/>
+      <c r="P122" s="2"/>
+      <c r="Q122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R122" s="2"/>
+      <c r="S122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="D123" s="2"/>
+      <c r="E123" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="F123" s="2"/>
+      <c r="G123" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="P123" s="2"/>
+      <c r="Q123" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R123" s="2"/>
+      <c r="S123" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="D124" s="2"/>
+      <c r="E124" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F124" s="2"/>
+      <c r="G124" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P124" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="Q124" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R124" s="2"/>
+      <c r="S124" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C125" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="D125" s="2"/>
+      <c r="E125" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F125" s="2"/>
+      <c r="G125" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="Q125" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R125" s="2"/>
+      <c r="S125" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="D126" s="2"/>
+      <c r="E126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F126" s="2"/>
+      <c r="G126" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="P126" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="Q126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R126" s="2"/>
+      <c r="S126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C127" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="D127" s="2"/>
+      <c r="E127" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F127" s="2"/>
+      <c r="G127" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="P127" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="Q127" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R127" s="2"/>
+      <c r="S127" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="D128" s="2"/>
+      <c r="E128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F128" s="2"/>
+      <c r="G128" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="P128" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="Q128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R128" s="2"/>
+      <c r="S128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C129" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="D129" s="2"/>
+      <c r="E129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F129" s="2"/>
+      <c r="G129" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="P129" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="Q129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R129" s="2"/>
+      <c r="S129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C130" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="D130" s="2"/>
+      <c r="E130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F130" s="2"/>
+      <c r="G130" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P130" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="Q130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R130" s="2"/>
+      <c r="S130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C131" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="D131" s="2"/>
+      <c r="E131" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F131" s="2"/>
+      <c r="G131" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="Q131" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R131" s="2"/>
+      <c r="S131" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="D132" s="2"/>
+      <c r="E132" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F132" s="2"/>
+      <c r="G132" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="P132" s="2"/>
+      <c r="Q132" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R132" s="2"/>
+      <c r="S132" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="Z132" s="2"/>
+      <c r="AA132" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C133" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="D133" s="2"/>
+      <c r="E133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F133" s="2"/>
+      <c r="G133" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="P133" s="2"/>
+      <c r="Q133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R133" s="2"/>
+      <c r="S133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="D134" s="2"/>
+      <c r="E134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F134" s="2"/>
+      <c r="G134" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O134" s="2"/>
+      <c r="P134" s="2"/>
+      <c r="Q134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R134" s="2"/>
+      <c r="S134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C135" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="D135" s="2"/>
+      <c r="E135" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="F135" s="2"/>
+      <c r="G135" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O135" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="P135" s="2"/>
+      <c r="Q135" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R135" s="2"/>
+      <c r="S135" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C136" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="D136" s="2"/>
+      <c r="E136" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="F136" s="2"/>
+      <c r="G136" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="P136" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="Q136" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R136" s="2"/>
+      <c r="S136" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="C137" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="D137" s="2"/>
+      <c r="E137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F137" s="2"/>
+      <c r="G137" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="P137" s="2"/>
+      <c r="Q137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R137" s="2"/>
+      <c r="S137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="C138" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="D138" s="2"/>
+      <c r="E138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F138" s="2"/>
+      <c r="G138" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O138" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="P138" s="2"/>
+      <c r="Q138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R138" s="2"/>
+      <c r="S138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="D139" s="2"/>
+      <c r="E139" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F139" s="2"/>
+      <c r="G139" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="O139" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="P139" s="2"/>
+      <c r="Q139" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R139" s="2"/>
+      <c r="S139" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C140" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="D140" s="2"/>
+      <c r="E140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F140" s="2"/>
+      <c r="G140" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="P140" s="2"/>
+      <c r="Q140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R140" s="2"/>
+      <c r="S140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="Z140" s="2"/>
+      <c r="AA140" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="C141" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="D141" s="2"/>
+      <c r="E141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F141" s="2"/>
+      <c r="G141" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="P141" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="Q141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R141" s="2"/>
+      <c r="S141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="Z141" s="2"/>
+      <c r="AA141" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK141" t="s" s="2">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="D142" s="2"/>
+      <c r="E142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F142" s="2"/>
+      <c r="G142" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="P142" s="2"/>
+      <c r="Q142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R142" s="2"/>
+      <c r="S142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C143" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="D143" s="2"/>
+      <c r="E143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F143" s="2"/>
+      <c r="G143" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="P143" s="2"/>
+      <c r="Q143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R143" s="2"/>
+      <c r="S143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AG143" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AH143" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI143" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AJ143" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK143" t="s" s="2">
+        <v>381</v>
       </c>
     </row>
   </sheetData>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-02T10:10:17+00:00</t>
+    <t>2023-10-02T11:49:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-02T11:49:05+00:00</t>
+    <t>2023-10-02T12:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-02T12:02:40+00:00</t>
+    <t>2023-10-03T08:22:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-03T08:22:32+00:00</t>
+    <t>2023-10-04T13:47:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-04T13:47:01+00:00</t>
+    <t>2023-10-05T12:28:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-05T12:28:13+00:00</t>
+    <t>2023-10-05T13:01:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-05T13:01:35+00:00</t>
+    <t>2023-10-06T10:30:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-06T10:30:12+00:00</t>
+    <t>2023-10-06T12:10:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-06T12:10:03+00:00</t>
+    <t>2023-10-06T14:30:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-06T14:30:45+00:00</t>
+    <t>2023-10-09T06:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/all-profiles.xlsx
+++ b/ig/specifications_techniques/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-09T06:42:29+00:00</t>
+    <t>2023-10-09T14:58:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
